--- a/data/tables/table_sex_specific_analysis.xlsx
+++ b/data/tables/table_sex_specific_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="313">
   <si>
     <t>Cassa</t>
   </si>
@@ -47,6 +47,9 @@
     <t>odds_ratio_pretty</t>
   </si>
   <si>
+    <t>99.0% CI</t>
+  </si>
+  <si>
     <t>p_value</t>
   </si>
   <si>
@@ -155,6 +158,78 @@
     <t>OR = 0.954</t>
   </si>
   <si>
+    <t>[1.080, 5.094]</t>
+  </si>
+  <si>
+    <t>[1.003, 1.062]</t>
+  </si>
+  <si>
+    <t>[-3.295, -0.026]</t>
+  </si>
+  <si>
+    <t>[0.408, 0.524]</t>
+  </si>
+  <si>
+    <t>[0.706, 5.546]</t>
+  </si>
+  <si>
+    <t>[0.931, 1.006]</t>
+  </si>
+  <si>
+    <t>[0.793, 3.681]</t>
+  </si>
+  <si>
+    <t>[0.900, 0.952]</t>
+  </si>
+  <si>
+    <t>[-2.989, -0.038]</t>
+  </si>
+  <si>
+    <t>[0.299, 0.406]</t>
+  </si>
+  <si>
+    <t>[0.334, 2.093]</t>
+  </si>
+  <si>
+    <t>[0.923, 0.985]</t>
+  </si>
+  <si>
+    <t>[2.327, 4.569]</t>
+  </si>
+  <si>
+    <t>[1.005, 1.061]</t>
+  </si>
+  <si>
+    <t>[-3.765, -2.266]</t>
+  </si>
+  <si>
+    <t>[0.402, 0.514]</t>
+  </si>
+  <si>
+    <t>[0.659, 1.778]</t>
+  </si>
+  <si>
+    <t>[0.931, 1.003]</t>
+  </si>
+  <si>
+    <t>[1.046, 2.186]</t>
+  </si>
+  <si>
+    <t>[0.901, 0.951]</t>
+  </si>
+  <si>
+    <t>[-3.627, -2.183]</t>
+  </si>
+  <si>
+    <t>[0.290, 0.394]</t>
+  </si>
+  <si>
+    <t>[0.503, 1.253]</t>
+  </si>
+  <si>
+    <t>[0.924, 0.984]</t>
+  </si>
+  <si>
     <t>childlessness</t>
   </si>
   <si>
@@ -242,6 +317,66 @@
     <t>OR = 0.945</t>
   </si>
   <si>
+    <t>[1.088, 1.406]</t>
+  </si>
+  <si>
+    <t>[1.002, 1.062]</t>
+  </si>
+  <si>
+    <t>[-0.665, -0.123]</t>
+  </si>
+  <si>
+    <t>[0.410, 0.528]</t>
+  </si>
+  <si>
+    <t>[0.930, 1.316]</t>
+  </si>
+  <si>
+    <t>[0.929, 1.004]</t>
+  </si>
+  <si>
+    <t>[0.912, 1.187]</t>
+  </si>
+  <si>
+    <t>[0.899, 0.952]</t>
+  </si>
+  <si>
+    <t>[-0.665, -0.166]</t>
+  </si>
+  <si>
+    <t>[0.286, 0.395]</t>
+  </si>
+  <si>
+    <t>[0.864, 1.172]</t>
+  </si>
+  <si>
+    <t>[0.922, 0.985]</t>
+  </si>
+  <si>
+    <t>[1.257, 1.514]</t>
+  </si>
+  <si>
+    <t>[1.005, 1.062]</t>
+  </si>
+  <si>
+    <t>[-1.129, -0.724]</t>
+  </si>
+  <si>
+    <t>[0.873, 1.144]</t>
+  </si>
+  <si>
+    <t>[1.004, 1.221]</t>
+  </si>
+  <si>
+    <t>[0.900, 0.951]</t>
+  </si>
+  <si>
+    <t>[-0.973, -0.595]</t>
+  </si>
+  <si>
+    <t>[0.840, 1.064]</t>
+  </si>
+  <si>
     <t>OR = 1.822</t>
   </si>
   <si>
@@ -287,6 +422,63 @@
     <t>OR = 0.812</t>
   </si>
   <si>
+    <t>[0.959, 3.460]</t>
+  </si>
+  <si>
+    <t>[1.004, 1.063]</t>
+  </si>
+  <si>
+    <t>[-2.476, 0.189]</t>
+  </si>
+  <si>
+    <t>[0.409, 0.524]</t>
+  </si>
+  <si>
+    <t>[0.992, 5.254]</t>
+  </si>
+  <si>
+    <t>[0.932, 1.007]</t>
+  </si>
+  <si>
+    <t>[0.960, 3.419]</t>
+  </si>
+  <si>
+    <t>[0.902, 0.954]</t>
+  </si>
+  <si>
+    <t>[-2.546, -0.095]</t>
+  </si>
+  <si>
+    <t>[0.299, 0.405]</t>
+  </si>
+  <si>
+    <t>[0.370, 1.710]</t>
+  </si>
+  <si>
+    <t>[0.925, 0.987]</t>
+  </si>
+  <si>
+    <t>[2.087, 3.892]</t>
+  </si>
+  <si>
+    <t>[-3.598, -2.237]</t>
+  </si>
+  <si>
+    <t>[0.718, 1.764]</t>
+  </si>
+  <si>
+    <t>[1.033, 1.996]</t>
+  </si>
+  <si>
+    <t>[-2.990, -1.713]</t>
+  </si>
+  <si>
+    <t>[0.543, 1.213]</t>
+  </si>
+  <si>
+    <t>[0.924, 0.985]</t>
+  </si>
+  <si>
     <t>OR = 1.997</t>
   </si>
   <si>
@@ -321,6 +513,63 @@
   </si>
   <si>
     <t>OR = 0.765</t>
+  </si>
+  <si>
+    <t>[1.094, 3.643]</t>
+  </si>
+  <si>
+    <t>[1.003, 1.061]</t>
+  </si>
+  <si>
+    <t>[-2.952, -0.433]</t>
+  </si>
+  <si>
+    <t>[0.405, 0.518]</t>
+  </si>
+  <si>
+    <t>[0.706, 3.587]</t>
+  </si>
+  <si>
+    <t>[0.932, 1.005]</t>
+  </si>
+  <si>
+    <t>[0.781, 2.640]</t>
+  </si>
+  <si>
+    <t>[0.902, 0.953]</t>
+  </si>
+  <si>
+    <t>[-3.154, -0.826]</t>
+  </si>
+  <si>
+    <t>[0.288, 0.393]</t>
+  </si>
+  <si>
+    <t>[0.515, 2.141]</t>
+  </si>
+  <si>
+    <t>[2.163, 3.939]</t>
+  </si>
+  <si>
+    <t>[-3.769, -2.423]</t>
+  </si>
+  <si>
+    <t>[0.609, 1.512]</t>
+  </si>
+  <si>
+    <t>[1.113, 2.108]</t>
+  </si>
+  <si>
+    <t>[-3.275, -2.009]</t>
+  </si>
+  <si>
+    <t>[0.289, 0.393]</t>
+  </si>
+  <si>
+    <t>[0.510, 1.147]</t>
+  </si>
+  <si>
+    <t>[0.925, 0.985]</t>
   </si>
   <si>
     <t>Info</t>
@@ -1062,10 +1311,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI27"/>
+  <dimension ref="A1:BM27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:61">
+    <row r="1" spans="1:65">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1084,10 +1333,10 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
@@ -1101,11 +1350,11 @@
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AG1" s="1"/>
-      <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
@@ -1118,12 +1367,12 @@
       <c r="AR1" s="1"/>
       <c r="AS1" s="1"/>
       <c r="AT1" s="1"/>
-      <c r="AU1" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="AU1" s="1"/>
       <c r="AV1" s="1"/>
       <c r="AW1" s="1"/>
-      <c r="AX1" s="1"/>
+      <c r="AX1" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="AY1" s="1"/>
       <c r="AZ1" s="1"/>
       <c r="BA1" s="1"/>
@@ -1135,8 +1384,12 @@
       <c r="BG1" s="1"/>
       <c r="BH1" s="1"/>
       <c r="BI1" s="1"/>
+      <c r="BJ1" s="1"/>
+      <c r="BK1" s="1"/>
+      <c r="BL1" s="1"/>
+      <c r="BM1" s="1"/>
     </row>
-    <row r="2" spans="1:61">
+    <row r="2" spans="1:65">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>4</v>
@@ -1184,148 +1437,160 @@
         <v>18</v>
       </c>
       <c r="Q2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="Y2" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="Z2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AC2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AD2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AF2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AG2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AI2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AJ2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AK2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AL2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="AM2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AN2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="AM2" s="1" t="s">
+      <c r="AO2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="AN2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AO2" s="1" t="s">
+      <c r="AP2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AQ2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AP2" s="1" t="s">
+      <c r="AR2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AQ2" s="1" t="s">
+      <c r="AS2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AR2" s="1" t="s">
+      <c r="AT2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AS2" s="1" t="s">
+      <c r="AU2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AT2" s="1" t="s">
+      <c r="AV2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AU2" s="1" t="s">
+      <c r="AW2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AX2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="AV2" s="1" t="s">
+      <c r="AY2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AW2" s="1" t="s">
+      <c r="AZ2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="AX2" s="1" t="s">
+      <c r="BA2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AY2" s="1" t="s">
+      <c r="BB2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AZ2" s="1" t="s">
+      <c r="BC2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="BA2" s="1" t="s">
+      <c r="BD2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="BB2" s="1" t="s">
+      <c r="BE2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="BC2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="BD2" s="1" t="s">
+      <c r="BF2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="BG2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="BE2" s="1" t="s">
+      <c r="BH2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="BF2" s="1" t="s">
+      <c r="BI2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="BG2" s="1" t="s">
+      <c r="BJ2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="BH2" s="1" t="s">
+      <c r="BK2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="BI2" s="1" t="s">
+      <c r="BL2" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="BM2" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="3" spans="1:61" hidden="1"/>
-    <row r="4" spans="1:61">
+    <row r="3" spans="1:65" hidden="1"/>
+    <row r="4" spans="1:65">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4">
         <v>0.8523285846669053</v>
@@ -1340,177 +1605,189 @@
         <v>5.094162705055759</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I4">
         <v>0.004654179812173109</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>0.05585015774607731</v>
       </c>
-      <c r="J4">
-        <v>12</v>
-      </c>
       <c r="K4">
+        <v>12</v>
+      </c>
+      <c r="L4">
         <v>163018</v>
       </c>
-      <c r="L4" t="s">
-        <v>46</v>
-      </c>
       <c r="M4" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="N4" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="O4" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="P4" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="Q4" t="s">
-        <v>19</v>
-      </c>
-      <c r="R4">
+        <v>83</v>
+      </c>
+      <c r="R4" t="s">
+        <v>20</v>
+      </c>
+      <c r="S4">
         <v>0.2124680217283457</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>1.23672656455489</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>1.088147969292687</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>1.405592473301158</v>
       </c>
-      <c r="V4" t="s">
-        <v>60</v>
-      </c>
-      <c r="W4">
+      <c r="W4" t="s">
+        <v>85</v>
+      </c>
+      <c r="X4" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y4">
         <v>1.903323018691617E-05</v>
       </c>
-      <c r="X4">
+      <c r="Z4">
         <v>0.0002283987622429941</v>
       </c>
-      <c r="Y4">
-        <v>12</v>
-      </c>
-      <c r="Z4">
+      <c r="AA4">
+        <v>12</v>
+      </c>
+      <c r="AB4">
         <v>155751</v>
       </c>
-      <c r="AA4" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>49</v>
-      </c>
       <c r="AC4" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="AD4" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="AE4" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="AF4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG4">
+        <v>77</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI4">
         <v>0.5998246897784437</v>
       </c>
-      <c r="AH4">
+      <c r="AJ4">
         <v>1.821799392338477</v>
       </c>
-      <c r="AI4">
+      <c r="AK4">
         <v>0.9592966436341909</v>
       </c>
-      <c r="AJ4">
+      <c r="AL4">
         <v>3.459777585952299</v>
       </c>
-      <c r="AK4" t="s">
-        <v>75</v>
-      </c>
-      <c r="AL4">
+      <c r="AM4" t="s">
+        <v>120</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>135</v>
+      </c>
+      <c r="AO4">
         <v>0.01599885953445674</v>
       </c>
-      <c r="AM4">
+      <c r="AP4">
         <v>0.1919863144134809</v>
       </c>
-      <c r="AN4">
-        <v>12</v>
-      </c>
-      <c r="AO4">
+      <c r="AQ4">
+        <v>12</v>
+      </c>
+      <c r="AR4">
         <v>163089</v>
       </c>
-      <c r="AP4" t="s">
-        <v>46</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>51</v>
-      </c>
       <c r="AS4" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="AT4" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="AU4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AV4">
+        <v>76</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>20</v>
+      </c>
+      <c r="AY4">
         <v>0.6915507562108965</v>
       </c>
-      <c r="AW4">
+      <c r="AZ4">
         <v>1.996809698516945</v>
       </c>
-      <c r="AX4">
+      <c r="BA4">
         <v>1.094448494467344</v>
       </c>
-      <c r="AY4">
+      <c r="BB4">
         <v>3.643158168015832</v>
       </c>
-      <c r="AZ4" t="s">
-        <v>90</v>
-      </c>
-      <c r="BA4">
+      <c r="BC4" t="s">
+        <v>154</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>166</v>
+      </c>
+      <c r="BE4">
         <v>0.003052096324431993</v>
       </c>
-      <c r="BB4">
+      <c r="BF4">
         <v>0.03662515589318392</v>
       </c>
-      <c r="BC4">
-        <v>12</v>
-      </c>
-      <c r="BD4">
+      <c r="BG4">
+        <v>12</v>
+      </c>
+      <c r="BH4">
         <v>169906</v>
       </c>
-      <c r="BE4" t="s">
-        <v>46</v>
-      </c>
-      <c r="BF4" t="s">
-        <v>49</v>
-      </c>
-      <c r="BG4" t="s">
-        <v>51</v>
-      </c>
-      <c r="BH4" t="s">
-        <v>52</v>
-      </c>
       <c r="BI4" t="s">
-        <v>58</v>
+        <v>71</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>74</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL4" t="s">
+        <v>77</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:61">
+    <row r="5" spans="1:65">
       <c r="A5" s="1">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5">
         <v>0.03158659350242339</v>
@@ -1525,177 +1802,189 @@
         <v>1.061794601560865</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5">
+        <v>24</v>
+      </c>
+      <c r="H5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5">
         <v>0.004137516105145585</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>0.04965019326174702</v>
       </c>
-      <c r="J5">
-        <v>12</v>
-      </c>
       <c r="K5">
+        <v>12</v>
+      </c>
+      <c r="L5">
         <v>163018</v>
       </c>
-      <c r="L5" t="s">
-        <v>46</v>
-      </c>
       <c r="M5" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="N5" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="O5" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="P5" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="Q5" t="s">
-        <v>20</v>
-      </c>
-      <c r="R5">
+        <v>83</v>
+      </c>
+      <c r="R5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S5">
         <v>0.03090347009221027</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>1.031385939491494</v>
       </c>
-      <c r="T5">
+      <c r="U5">
         <v>1.001891382720335</v>
       </c>
-      <c r="U5">
+      <c r="V5">
         <v>1.061748782879478</v>
       </c>
-      <c r="V5" t="s">
-        <v>61</v>
-      </c>
-      <c r="W5">
+      <c r="W5" t="s">
+        <v>86</v>
+      </c>
+      <c r="X5" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y5">
         <v>0.006077208959743133</v>
       </c>
-      <c r="X5">
+      <c r="Z5">
         <v>0.07292650751691759</v>
       </c>
-      <c r="Y5">
-        <v>12</v>
-      </c>
-      <c r="Z5">
+      <c r="AA5">
+        <v>12</v>
+      </c>
+      <c r="AB5">
         <v>155751</v>
       </c>
-      <c r="AA5" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>49</v>
-      </c>
       <c r="AC5" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="AD5" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="AE5" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="AF5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG5">
+        <v>77</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI5">
         <v>0.03254006317370441</v>
       </c>
-      <c r="AH5">
+      <c r="AJ5">
         <v>1.033075280589327</v>
       </c>
-      <c r="AI5">
+      <c r="AK5">
         <v>1.00416734883879</v>
       </c>
-      <c r="AJ5">
+      <c r="AL5">
         <v>1.062815412788385</v>
       </c>
-      <c r="AK5" t="s">
-        <v>35</v>
-      </c>
-      <c r="AL5">
+      <c r="AM5" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>136</v>
+      </c>
+      <c r="AO5">
         <v>0.00314434398442395</v>
       </c>
-      <c r="AM5">
+      <c r="AP5">
         <v>0.0377321278130874</v>
       </c>
-      <c r="AN5">
-        <v>12</v>
-      </c>
-      <c r="AO5">
+      <c r="AQ5">
+        <v>12</v>
+      </c>
+      <c r="AR5">
         <v>163089</v>
       </c>
-      <c r="AP5" t="s">
-        <v>46</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>49</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>51</v>
-      </c>
       <c r="AS5" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="AT5" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="AU5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AV5">
+        <v>76</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>77</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>83</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY5">
         <v>0.03114402049634412</v>
       </c>
-      <c r="AW5">
+      <c r="AZ5">
         <v>1.031634069638764</v>
       </c>
-      <c r="AX5">
+      <c r="BA5">
         <v>1.003357454350132</v>
       </c>
-      <c r="AY5">
+      <c r="BB5">
         <v>1.060707576372927</v>
       </c>
-      <c r="AZ5" t="s">
-        <v>23</v>
-      </c>
-      <c r="BA5">
+      <c r="BC5" t="s">
+        <v>24</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>167</v>
+      </c>
+      <c r="BE5">
         <v>0.003895739172296256</v>
       </c>
-      <c r="BB5">
+      <c r="BF5">
         <v>0.04674887006755507</v>
       </c>
-      <c r="BC5">
-        <v>12</v>
-      </c>
-      <c r="BD5">
+      <c r="BG5">
+        <v>12</v>
+      </c>
+      <c r="BH5">
         <v>169906</v>
       </c>
-      <c r="BE5" t="s">
-        <v>46</v>
-      </c>
-      <c r="BF5" t="s">
-        <v>49</v>
-      </c>
-      <c r="BG5" t="s">
-        <v>51</v>
-      </c>
-      <c r="BH5" t="s">
-        <v>52</v>
-      </c>
       <c r="BI5" t="s">
-        <v>58</v>
+        <v>71</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>74</v>
+      </c>
+      <c r="BK5" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL5" t="s">
+        <v>77</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:61">
+    <row r="6" spans="1:65">
       <c r="A6" s="1">
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6">
         <v>-1.660746231286808</v>
@@ -1710,177 +1999,189 @@
         <v>0.9741723966824857</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6">
+        <v>25</v>
+      </c>
+      <c r="H6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6">
         <v>0.008868965866351769</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>0.1064275903962212</v>
       </c>
-      <c r="J6">
-        <v>12</v>
-      </c>
       <c r="K6">
+        <v>12</v>
+      </c>
+      <c r="L6">
         <v>162902</v>
       </c>
-      <c r="L6" t="s">
-        <v>47</v>
-      </c>
       <c r="M6" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="N6" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="O6" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="P6" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="Q6" t="s">
-        <v>19</v>
-      </c>
-      <c r="R6">
+        <v>84</v>
+      </c>
+      <c r="R6" t="s">
+        <v>20</v>
+      </c>
+      <c r="S6">
         <v>-0.3942848277789848</v>
       </c>
-      <c r="S6">
+      <c r="T6">
         <v>0.6741620088238738</v>
       </c>
-      <c r="T6">
+      <c r="U6">
         <v>0.5141610188875372</v>
       </c>
-      <c r="U6">
+      <c r="V6">
         <v>0.8839534648597168</v>
       </c>
-      <c r="V6" t="s">
-        <v>62</v>
-      </c>
-      <c r="W6">
+      <c r="W6" t="s">
+        <v>87</v>
+      </c>
+      <c r="X6" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y6">
         <v>0.0001778575645279379</v>
       </c>
-      <c r="X6">
+      <c r="Z6">
         <v>0.002134290774335255</v>
       </c>
-      <c r="Y6">
-        <v>12</v>
-      </c>
-      <c r="Z6">
+      <c r="AA6">
+        <v>12</v>
+      </c>
+      <c r="AB6">
         <v>155631</v>
       </c>
-      <c r="AA6" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>49</v>
-      </c>
       <c r="AC6" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="AD6" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="AE6" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="AF6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG6">
+        <v>78</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI6">
         <v>-1.143529996853262</v>
       </c>
-      <c r="AH6">
+      <c r="AJ6">
         <v>0.3186920519459794</v>
       </c>
-      <c r="AI6">
+      <c r="AK6">
         <v>0.08409489461559427</v>
       </c>
-      <c r="AJ6">
+      <c r="AL6">
         <v>1.207738287060116</v>
       </c>
-      <c r="AK6" t="s">
-        <v>76</v>
-      </c>
-      <c r="AL6">
+      <c r="AM6" t="s">
+        <v>121</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>137</v>
+      </c>
+      <c r="AO6">
         <v>0.02704268476549606</v>
       </c>
-      <c r="AM6">
+      <c r="AP6">
         <v>0.3245122171859527</v>
       </c>
-      <c r="AN6">
-        <v>12</v>
-      </c>
-      <c r="AO6">
+      <c r="AQ6">
+        <v>12</v>
+      </c>
+      <c r="AR6">
         <v>162973</v>
       </c>
-      <c r="AP6" t="s">
-        <v>47</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>49</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>51</v>
-      </c>
       <c r="AS6" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="AT6" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="AU6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AV6">
+        <v>76</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>20</v>
+      </c>
+      <c r="AY6">
         <v>-1.692759714746228</v>
       </c>
-      <c r="AW6">
+      <c r="AZ6">
         <v>0.1840110047484291</v>
       </c>
-      <c r="AX6">
+      <c r="BA6">
         <v>0.05221048476960594</v>
       </c>
-      <c r="AY6">
+      <c r="BB6">
         <v>0.6485296970128472</v>
       </c>
-      <c r="AZ6" t="s">
-        <v>91</v>
-      </c>
-      <c r="BA6">
+      <c r="BC6" t="s">
+        <v>155</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>168</v>
+      </c>
+      <c r="BE6">
         <v>0.0005375446501879972</v>
       </c>
-      <c r="BB6">
+      <c r="BF6">
         <v>0.006450535802255967</v>
       </c>
-      <c r="BC6">
-        <v>12</v>
-      </c>
-      <c r="BD6">
+      <c r="BG6">
+        <v>12</v>
+      </c>
+      <c r="BH6">
         <v>169798</v>
       </c>
-      <c r="BE6" t="s">
-        <v>47</v>
-      </c>
-      <c r="BF6" t="s">
-        <v>49</v>
-      </c>
-      <c r="BG6" t="s">
-        <v>51</v>
-      </c>
-      <c r="BH6" t="s">
-        <v>53</v>
-      </c>
       <c r="BI6" t="s">
-        <v>59</v>
+        <v>72</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>74</v>
+      </c>
+      <c r="BK6" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL6" t="s">
+        <v>78</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="7" spans="1:61">
+    <row r="7" spans="1:65">
       <c r="A7" s="1">
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7">
         <v>0.4660320918538042</v>
@@ -1895,177 +2196,189 @@
         <v>1.688482530633116</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7">
+        <v>26</v>
+      </c>
+      <c r="H7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7">
         <v>8.226519888667335E-96</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>9.871823866400801E-95</v>
       </c>
-      <c r="J7">
-        <v>12</v>
-      </c>
       <c r="K7">
+        <v>12</v>
+      </c>
+      <c r="L7">
         <v>162902</v>
       </c>
-      <c r="L7" t="s">
-        <v>47</v>
-      </c>
       <c r="M7" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="N7" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="O7" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="P7" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="Q7" t="s">
-        <v>20</v>
-      </c>
-      <c r="R7">
+        <v>84</v>
+      </c>
+      <c r="R7" t="s">
+        <v>21</v>
+      </c>
+      <c r="S7">
         <v>0.4689863051940806</v>
       </c>
-      <c r="S7">
+      <c r="T7">
         <v>1.598373109195237</v>
       </c>
-      <c r="T7">
+      <c r="U7">
         <v>1.506618399817201</v>
       </c>
-      <c r="U7">
+      <c r="V7">
         <v>1.695715780789896</v>
       </c>
-      <c r="V7" t="s">
-        <v>63</v>
-      </c>
-      <c r="W7">
+      <c r="W7" t="s">
+        <v>88</v>
+      </c>
+      <c r="X7" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y7">
         <v>8.342786929605638E-93</v>
       </c>
-      <c r="X7">
+      <c r="Z7">
         <v>1.001134431552677E-91</v>
       </c>
-      <c r="Y7">
-        <v>12</v>
-      </c>
-      <c r="Z7">
+      <c r="AA7">
+        <v>12</v>
+      </c>
+      <c r="AB7">
         <v>155631</v>
       </c>
-      <c r="AA7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>49</v>
-      </c>
       <c r="AC7" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="AD7" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="AE7" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="AF7" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG7">
+        <v>78</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI7">
         <v>0.4662936823673795</v>
       </c>
-      <c r="AH7">
+      <c r="AJ7">
         <v>1.594075082355224</v>
       </c>
-      <c r="AI7">
+      <c r="AK7">
         <v>1.504563137033339</v>
       </c>
-      <c r="AJ7">
+      <c r="AL7">
         <v>1.688912419585293</v>
       </c>
-      <c r="AK7" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL7">
+      <c r="AM7" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO7">
         <v>6.122752842153162E-96</v>
       </c>
-      <c r="AM7">
+      <c r="AP7">
         <v>7.347303410583794E-95</v>
       </c>
-      <c r="AN7">
-        <v>12</v>
-      </c>
-      <c r="AO7">
+      <c r="AQ7">
+        <v>12</v>
+      </c>
+      <c r="AR7">
         <v>162973</v>
       </c>
-      <c r="AP7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>49</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>51</v>
-      </c>
       <c r="AS7" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="AT7" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="AU7" t="s">
-        <v>20</v>
-      </c>
-      <c r="AV7">
+        <v>76</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY7">
         <v>0.4612641334665646</v>
       </c>
-      <c r="AW7">
+      <c r="AZ7">
         <v>1.58607773216752</v>
       </c>
-      <c r="AX7">
+      <c r="BA7">
         <v>1.498779196401157</v>
       </c>
-      <c r="AY7">
+      <c r="BB7">
         <v>1.678461095882689</v>
       </c>
-      <c r="AZ7" t="s">
-        <v>92</v>
-      </c>
-      <c r="BA7">
+      <c r="BC7" t="s">
+        <v>156</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>169</v>
+      </c>
+      <c r="BE7">
         <v>8.635011632346715E-98</v>
       </c>
-      <c r="BB7">
+      <c r="BF7">
         <v>1.036201395881606E-96</v>
       </c>
-      <c r="BC7">
-        <v>12</v>
-      </c>
-      <c r="BD7">
+      <c r="BG7">
+        <v>12</v>
+      </c>
+      <c r="BH7">
         <v>169798</v>
       </c>
-      <c r="BE7" t="s">
-        <v>47</v>
-      </c>
-      <c r="BF7" t="s">
-        <v>49</v>
-      </c>
-      <c r="BG7" t="s">
-        <v>51</v>
-      </c>
-      <c r="BH7" t="s">
-        <v>53</v>
-      </c>
       <c r="BI7" t="s">
-        <v>59</v>
+        <v>72</v>
+      </c>
+      <c r="BJ7" t="s">
+        <v>74</v>
+      </c>
+      <c r="BK7" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL7" t="s">
+        <v>78</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="8" spans="1:61">
+    <row r="8" spans="1:65">
       <c r="A8" s="1">
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8">
         <v>0.682240330574836</v>
@@ -2080,177 +2393,189 @@
         <v>5.546057056827697</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8">
+        <v>27</v>
+      </c>
+      <c r="H8" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8">
         <v>0.08824135440334896</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>1.058896252840188</v>
       </c>
-      <c r="J8">
-        <v>12</v>
-      </c>
       <c r="K8">
+        <v>12</v>
+      </c>
+      <c r="L8">
         <v>163959</v>
       </c>
-      <c r="L8" t="s">
-        <v>48</v>
-      </c>
       <c r="M8" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="N8" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="O8" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="P8" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="Q8" t="s">
-        <v>19</v>
-      </c>
-      <c r="R8">
+        <v>83</v>
+      </c>
+      <c r="R8" t="s">
+        <v>20</v>
+      </c>
+      <c r="S8">
         <v>0.1009887105124187</v>
       </c>
-      <c r="S8">
+      <c r="T8">
         <v>1.106264152537513</v>
       </c>
-      <c r="T8">
+      <c r="U8">
         <v>0.9297469126353478</v>
       </c>
-      <c r="U8">
+      <c r="V8">
         <v>1.316294099563773</v>
       </c>
-      <c r="V8" t="s">
-        <v>64</v>
-      </c>
-      <c r="W8">
+      <c r="W8" t="s">
+        <v>89</v>
+      </c>
+      <c r="X8" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y8">
         <v>0.1345373031934903</v>
       </c>
-      <c r="X8">
+      <c r="Z8">
         <v>1.614447638321884</v>
       </c>
-      <c r="Y8">
-        <v>12</v>
-      </c>
-      <c r="Z8">
+      <c r="AA8">
+        <v>12</v>
+      </c>
+      <c r="AB8">
         <v>156637</v>
       </c>
-      <c r="AA8" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>49</v>
-      </c>
       <c r="AC8" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="AD8" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="AE8" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="AF8" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG8">
+        <v>79</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI8">
         <v>0.8256982620948048</v>
       </c>
-      <c r="AH8">
+      <c r="AJ8">
         <v>2.283474672590347</v>
       </c>
-      <c r="AI8">
+      <c r="AK8">
         <v>0.9923581182285701</v>
       </c>
-      <c r="AJ8">
+      <c r="AL8">
         <v>5.254410161595102</v>
       </c>
-      <c r="AK8" t="s">
-        <v>77</v>
-      </c>
-      <c r="AL8">
+      <c r="AM8" t="s">
+        <v>122</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>139</v>
+      </c>
+      <c r="AO8">
         <v>0.01070700662108193</v>
       </c>
-      <c r="AM8">
+      <c r="AP8">
         <v>0.1284840794529831</v>
       </c>
-      <c r="AN8">
-        <v>12</v>
-      </c>
-      <c r="AO8">
+      <c r="AQ8">
+        <v>12</v>
+      </c>
+      <c r="AR8">
         <v>164028</v>
       </c>
-      <c r="AP8" t="s">
-        <v>48</v>
-      </c>
-      <c r="AQ8" t="s">
-        <v>49</v>
-      </c>
-      <c r="AR8" t="s">
-        <v>51</v>
-      </c>
       <c r="AS8" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="AT8" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="AU8" t="s">
-        <v>19</v>
-      </c>
-      <c r="AV8">
+        <v>76</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>83</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>20</v>
+      </c>
+      <c r="AY8">
         <v>0.4647936003095065</v>
       </c>
-      <c r="AW8">
+      <c r="AZ8">
         <v>1.591685631559485</v>
       </c>
-      <c r="AX8">
+      <c r="BA8">
         <v>0.7063367286199851</v>
       </c>
-      <c r="AY8">
+      <c r="BB8">
         <v>3.586763999463408</v>
       </c>
-      <c r="AZ8" t="s">
-        <v>93</v>
-      </c>
-      <c r="BA8">
+      <c r="BC8" t="s">
+        <v>157</v>
+      </c>
+      <c r="BD8" t="s">
+        <v>170</v>
+      </c>
+      <c r="BE8">
         <v>0.1405917648288251</v>
       </c>
-      <c r="BB8">
+      <c r="BF8">
         <v>1.687101177945901</v>
       </c>
-      <c r="BC8">
-        <v>12</v>
-      </c>
-      <c r="BD8">
+      <c r="BG8">
+        <v>12</v>
+      </c>
+      <c r="BH8">
         <v>170888</v>
       </c>
-      <c r="BE8" t="s">
-        <v>48</v>
-      </c>
-      <c r="BF8" t="s">
-        <v>49</v>
-      </c>
-      <c r="BG8" t="s">
-        <v>51</v>
-      </c>
-      <c r="BH8" t="s">
-        <v>54</v>
-      </c>
       <c r="BI8" t="s">
-        <v>58</v>
+        <v>73</v>
+      </c>
+      <c r="BJ8" t="s">
+        <v>74</v>
+      </c>
+      <c r="BK8" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL8" t="s">
+        <v>79</v>
+      </c>
+      <c r="BM8" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:61">
+    <row r="9" spans="1:65">
       <c r="A9" s="1">
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9">
         <v>-0.03277727773264067</v>
@@ -2265,177 +2590,189 @@
         <v>1.005514585020086</v>
       </c>
       <c r="G9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9">
         <v>0.02740185199623635</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>0.3288222239548362</v>
       </c>
-      <c r="J9">
-        <v>12</v>
-      </c>
       <c r="K9">
+        <v>12</v>
+      </c>
+      <c r="L9">
         <v>163959</v>
       </c>
-      <c r="L9" t="s">
-        <v>48</v>
-      </c>
       <c r="M9" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="N9" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="O9" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="P9" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="Q9" t="s">
-        <v>20</v>
-      </c>
-      <c r="R9">
+        <v>83</v>
+      </c>
+      <c r="R9" t="s">
+        <v>21</v>
+      </c>
+      <c r="S9">
         <v>-0.03485435422810796</v>
       </c>
-      <c r="S9">
+      <c r="T9">
         <v>0.9657460628458022</v>
       </c>
-      <c r="T9">
+      <c r="U9">
         <v>0.9286634741717629</v>
       </c>
-      <c r="U9">
+      <c r="V9">
         <v>1.004309401458881</v>
       </c>
-      <c r="V9" t="s">
-        <v>39</v>
-      </c>
-      <c r="W9">
+      <c r="W9" t="s">
+        <v>40</v>
+      </c>
+      <c r="X9" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y9">
         <v>0.02185152559758251</v>
       </c>
-      <c r="X9">
+      <c r="Z9">
         <v>0.2622183071709902</v>
       </c>
-      <c r="Y9">
-        <v>12</v>
-      </c>
-      <c r="Z9">
+      <c r="AA9">
+        <v>12</v>
+      </c>
+      <c r="AB9">
         <v>156637</v>
       </c>
-      <c r="AA9" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>49</v>
-      </c>
       <c r="AC9" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="AD9" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="AE9" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="AF9" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG9">
+        <v>79</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI9">
         <v>-0.03159807716075619</v>
       </c>
-      <c r="AH9">
+      <c r="AJ9">
         <v>0.9688959252322047</v>
       </c>
-      <c r="AI9">
+      <c r="AK9">
         <v>0.9324945769203979</v>
       </c>
-      <c r="AJ9">
+      <c r="AL9">
         <v>1.006718255704887</v>
       </c>
-      <c r="AK9" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL9">
+      <c r="AM9" t="s">
+        <v>123</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>140</v>
+      </c>
+      <c r="AO9">
         <v>0.03355004918856815</v>
       </c>
-      <c r="AM9">
+      <c r="AP9">
         <v>0.4026005902628178</v>
       </c>
-      <c r="AN9">
-        <v>12</v>
-      </c>
-      <c r="AO9">
+      <c r="AQ9">
+        <v>12</v>
+      </c>
+      <c r="AR9">
         <v>164028</v>
       </c>
-      <c r="AP9" t="s">
-        <v>48</v>
-      </c>
-      <c r="AQ9" t="s">
-        <v>49</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>51</v>
-      </c>
       <c r="AS9" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="AT9" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="AU9" t="s">
-        <v>20</v>
-      </c>
-      <c r="AV9">
+        <v>76</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY9">
         <v>-0.03270227859867903</v>
       </c>
-      <c r="AW9">
+      <c r="AZ9">
         <v>0.967826659409438</v>
       </c>
-      <c r="AX9">
+      <c r="BA9">
         <v>0.9321299732835348</v>
       </c>
-      <c r="AY9">
+      <c r="BB9">
         <v>1.004890379572325</v>
       </c>
-      <c r="AZ9" t="s">
-        <v>27</v>
-      </c>
-      <c r="BA9">
+      <c r="BC9" t="s">
+        <v>28</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>171</v>
+      </c>
+      <c r="BE9">
         <v>0.02499670006728925</v>
       </c>
-      <c r="BB9">
+      <c r="BF9">
         <v>0.299960400807471</v>
       </c>
-      <c r="BC9">
-        <v>12</v>
-      </c>
-      <c r="BD9">
+      <c r="BG9">
+        <v>12</v>
+      </c>
+      <c r="BH9">
         <v>170888</v>
       </c>
-      <c r="BE9" t="s">
-        <v>48</v>
-      </c>
-      <c r="BF9" t="s">
-        <v>49</v>
-      </c>
-      <c r="BG9" t="s">
-        <v>51</v>
-      </c>
-      <c r="BH9" t="s">
-        <v>54</v>
-      </c>
       <c r="BI9" t="s">
-        <v>58</v>
+        <v>73</v>
+      </c>
+      <c r="BJ9" t="s">
+        <v>74</v>
+      </c>
+      <c r="BK9" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL9" t="s">
+        <v>79</v>
+      </c>
+      <c r="BM9" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:61">
+    <row r="10" spans="1:65">
       <c r="A10" s="1">
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10">
         <v>0.5358863147158361</v>
@@ -2450,177 +2787,189 @@
         <v>3.681131045959624</v>
       </c>
       <c r="G10" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10">
+        <v>29</v>
+      </c>
+      <c r="H10" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10">
         <v>0.07203552978947701</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>0.8644263574737241</v>
       </c>
-      <c r="J10">
-        <v>12</v>
-      </c>
       <c r="K10">
+        <v>12</v>
+      </c>
+      <c r="L10">
         <v>190228</v>
       </c>
-      <c r="L10" t="s">
-        <v>46</v>
-      </c>
       <c r="M10" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="N10" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="O10" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="P10" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="Q10" t="s">
-        <v>19</v>
-      </c>
-      <c r="R10">
+        <v>83</v>
+      </c>
+      <c r="R10" t="s">
+        <v>20</v>
+      </c>
+      <c r="S10">
         <v>0.03987062838137025</v>
       </c>
-      <c r="S10">
+      <c r="T10">
         <v>1.040676131527501</v>
       </c>
-      <c r="T10">
+      <c r="U10">
         <v>0.9122565701910001</v>
       </c>
-      <c r="U10">
+      <c r="V10">
         <v>1.187173483995072</v>
       </c>
-      <c r="V10" t="s">
-        <v>65</v>
-      </c>
-      <c r="W10">
+      <c r="W10" t="s">
+        <v>90</v>
+      </c>
+      <c r="X10" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y10">
         <v>0.4355235244756029</v>
       </c>
-      <c r="X10">
+      <c r="Z10">
         <v>5.226282293707236</v>
       </c>
-      <c r="Y10">
-        <v>12</v>
-      </c>
-      <c r="Z10">
+      <c r="AA10">
+        <v>12</v>
+      </c>
+      <c r="AB10">
         <v>181728</v>
       </c>
-      <c r="AA10" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>50</v>
-      </c>
       <c r="AC10" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="AD10" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="AE10" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="AF10" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG10">
+        <v>77</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI10">
         <v>0.5941180583956855</v>
       </c>
-      <c r="AH10">
+      <c r="AJ10">
         <v>1.81143266243941</v>
       </c>
-      <c r="AI10">
+      <c r="AK10">
         <v>0.9596068469127207</v>
       </c>
-      <c r="AJ10">
+      <c r="AL10">
         <v>3.419409001831323</v>
       </c>
-      <c r="AK10" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL10">
+      <c r="AM10" t="s">
+        <v>124</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>141</v>
+      </c>
+      <c r="AO10">
         <v>0.01601083591924998</v>
       </c>
-      <c r="AM10">
+      <c r="AP10">
         <v>0.1921300310309997</v>
       </c>
-      <c r="AN10">
-        <v>12</v>
-      </c>
-      <c r="AO10">
+      <c r="AQ10">
+        <v>12</v>
+      </c>
+      <c r="AR10">
         <v>190336</v>
       </c>
-      <c r="AP10" t="s">
-        <v>46</v>
-      </c>
-      <c r="AQ10" t="s">
-        <v>50</v>
-      </c>
-      <c r="AR10" t="s">
-        <v>51</v>
-      </c>
       <c r="AS10" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="AT10" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="AU10" t="s">
-        <v>19</v>
-      </c>
-      <c r="AV10">
+        <v>76</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>83</v>
+      </c>
+      <c r="AX10" t="s">
+        <v>20</v>
+      </c>
+      <c r="AY10">
         <v>0.3618515401259677</v>
       </c>
-      <c r="AW10">
+      <c r="AZ10">
         <v>1.435985739872712</v>
       </c>
-      <c r="AX10">
+      <c r="BA10">
         <v>0.7810393502685173</v>
       </c>
-      <c r="AY10">
+      <c r="BB10">
         <v>2.64014232369836</v>
       </c>
-      <c r="AZ10" t="s">
-        <v>87</v>
-      </c>
-      <c r="BA10">
+      <c r="BC10" t="s">
+        <v>132</v>
+      </c>
+      <c r="BD10" t="s">
+        <v>172</v>
+      </c>
+      <c r="BE10">
         <v>0.1258841019214741</v>
       </c>
-      <c r="BB10">
+      <c r="BF10">
         <v>1.510609223057689</v>
       </c>
-      <c r="BC10">
-        <v>12</v>
-      </c>
-      <c r="BD10">
+      <c r="BG10">
+        <v>12</v>
+      </c>
+      <c r="BH10">
         <v>198318</v>
       </c>
-      <c r="BE10" t="s">
-        <v>46</v>
-      </c>
-      <c r="BF10" t="s">
-        <v>50</v>
-      </c>
-      <c r="BG10" t="s">
-        <v>51</v>
-      </c>
-      <c r="BH10" t="s">
-        <v>52</v>
-      </c>
       <c r="BI10" t="s">
-        <v>58</v>
+        <v>71</v>
+      </c>
+      <c r="BJ10" t="s">
+        <v>75</v>
+      </c>
+      <c r="BK10" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL10" t="s">
+        <v>77</v>
+      </c>
+      <c r="BM10" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:61">
+    <row r="11" spans="1:65">
       <c r="A11" s="1">
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11">
         <v>-0.07699246790490626</v>
@@ -2635,177 +2984,189 @@
         <v>0.9521245174699385</v>
       </c>
       <c r="G11" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11">
+        <v>30</v>
+      </c>
+      <c r="H11" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11">
         <v>1.249160481352101E-12</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>1.498992577622521E-11</v>
       </c>
-      <c r="J11">
-        <v>12</v>
-      </c>
       <c r="K11">
+        <v>12</v>
+      </c>
+      <c r="L11">
         <v>190228</v>
       </c>
-      <c r="L11" t="s">
-        <v>46</v>
-      </c>
       <c r="M11" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="N11" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="O11" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="P11" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="Q11" t="s">
-        <v>20</v>
-      </c>
-      <c r="R11">
+        <v>83</v>
+      </c>
+      <c r="R11" t="s">
+        <v>21</v>
+      </c>
+      <c r="S11">
         <v>-0.07760377888244691</v>
       </c>
-      <c r="S11">
+      <c r="T11">
         <v>0.9253309895975371</v>
       </c>
-      <c r="T11">
+      <c r="U11">
         <v>0.8992660810415176</v>
       </c>
-      <c r="U11">
+      <c r="V11">
         <v>0.9521513802876617</v>
       </c>
-      <c r="V11" t="s">
-        <v>41</v>
-      </c>
-      <c r="W11">
+      <c r="W11" t="s">
+        <v>42</v>
+      </c>
+      <c r="X11" t="s">
+        <v>107</v>
+      </c>
+      <c r="Y11">
         <v>2.633319058488761E-12</v>
       </c>
-      <c r="X11">
+      <c r="Z11">
         <v>3.159982870186513E-11</v>
       </c>
-      <c r="Y11">
-        <v>12</v>
-      </c>
-      <c r="Z11">
+      <c r="AA11">
+        <v>12</v>
+      </c>
+      <c r="AB11">
         <v>181728</v>
       </c>
-      <c r="AA11" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>50</v>
-      </c>
       <c r="AC11" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="AD11" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="AE11" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="AF11" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG11">
+        <v>77</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI11">
         <v>-0.07539085966924811</v>
       </c>
-      <c r="AH11">
+      <c r="AJ11">
         <v>0.9273809396733879</v>
       </c>
-      <c r="AI11">
+      <c r="AK11">
         <v>0.9018317388754324</v>
       </c>
-      <c r="AJ11">
+      <c r="AL11">
         <v>0.9536539580453712</v>
       </c>
-      <c r="AK11" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL11">
+      <c r="AM11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>142</v>
+      </c>
+      <c r="AO11">
         <v>3.620015211568588E-12</v>
       </c>
-      <c r="AM11">
+      <c r="AP11">
         <v>4.344018253882306E-11</v>
       </c>
-      <c r="AN11">
-        <v>12</v>
-      </c>
-      <c r="AO11">
+      <c r="AQ11">
+        <v>12</v>
+      </c>
+      <c r="AR11">
         <v>190336</v>
       </c>
-      <c r="AP11" t="s">
-        <v>46</v>
-      </c>
-      <c r="AQ11" t="s">
-        <v>50</v>
-      </c>
-      <c r="AR11" t="s">
-        <v>51</v>
-      </c>
       <c r="AS11" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="AT11" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="AU11" t="s">
-        <v>20</v>
-      </c>
-      <c r="AV11">
+        <v>76</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>83</v>
+      </c>
+      <c r="AX11" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY11">
         <v>-0.07579465775131596</v>
       </c>
-      <c r="AW11">
+      <c r="AZ11">
         <v>0.9270065406244976</v>
       </c>
-      <c r="AX11">
+      <c r="BA11">
         <v>0.9020057619876484</v>
       </c>
-      <c r="AY11">
+      <c r="BB11">
         <v>0.9527002626534948</v>
       </c>
-      <c r="AZ11" t="s">
-        <v>80</v>
-      </c>
-      <c r="BA11">
+      <c r="BC11" t="s">
+        <v>125</v>
+      </c>
+      <c r="BD11" t="s">
+        <v>173</v>
+      </c>
+      <c r="BE11">
         <v>9.262455189646431E-13</v>
       </c>
-      <c r="BB11">
+      <c r="BF11">
         <v>1.111494622757572E-11</v>
       </c>
-      <c r="BC11">
-        <v>12</v>
-      </c>
-      <c r="BD11">
+      <c r="BG11">
+        <v>12</v>
+      </c>
+      <c r="BH11">
         <v>198318</v>
       </c>
-      <c r="BE11" t="s">
-        <v>46</v>
-      </c>
-      <c r="BF11" t="s">
-        <v>50</v>
-      </c>
-      <c r="BG11" t="s">
-        <v>51</v>
-      </c>
-      <c r="BH11" t="s">
-        <v>52</v>
-      </c>
       <c r="BI11" t="s">
-        <v>58</v>
+        <v>71</v>
+      </c>
+      <c r="BJ11" t="s">
+        <v>75</v>
+      </c>
+      <c r="BK11" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL11" t="s">
+        <v>77</v>
+      </c>
+      <c r="BM11" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="12" spans="1:61">
+    <row r="12" spans="1:65">
       <c r="A12" s="1">
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>-1.513250660407001</v>
@@ -2820,177 +3181,189 @@
         <v>0.9628531291880804</v>
       </c>
       <c r="G12" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12">
+        <v>31</v>
+      </c>
+      <c r="H12" t="s">
+        <v>55</v>
+      </c>
+      <c r="I12">
         <v>0.008243810481444926</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>0.09892572577733912</v>
       </c>
-      <c r="J12">
-        <v>12</v>
-      </c>
       <c r="K12">
+        <v>12</v>
+      </c>
+      <c r="L12">
         <v>188699</v>
       </c>
-      <c r="L12" t="s">
-        <v>47</v>
-      </c>
       <c r="M12" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="N12" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="O12" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="P12" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="Q12" t="s">
-        <v>19</v>
-      </c>
-      <c r="R12">
+        <v>84</v>
+      </c>
+      <c r="R12" t="s">
+        <v>20</v>
+      </c>
+      <c r="S12">
         <v>-0.4154528612880441</v>
       </c>
-      <c r="S12">
+      <c r="T12">
         <v>0.6600413058570923</v>
       </c>
-      <c r="T12">
+      <c r="U12">
         <v>0.5144388374822629</v>
       </c>
-      <c r="U12">
+      <c r="V12">
         <v>0.8468538797919907</v>
       </c>
-      <c r="V12" t="s">
-        <v>66</v>
-      </c>
-      <c r="W12">
+      <c r="W12" t="s">
+        <v>91</v>
+      </c>
+      <c r="X12" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y12">
         <v>1.756085023767216E-05</v>
       </c>
-      <c r="X12">
+      <c r="Z12">
         <v>0.0002107302028520659</v>
       </c>
-      <c r="Y12">
-        <v>12</v>
-      </c>
-      <c r="Z12">
+      <c r="AA12">
+        <v>12</v>
+      </c>
+      <c r="AB12">
         <v>180261</v>
       </c>
-      <c r="AA12" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>50</v>
-      </c>
       <c r="AC12" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="AD12" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="AE12" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="AF12" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG12">
+        <v>78</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI12">
         <v>-1.320520129254024</v>
       </c>
-      <c r="AH12">
+      <c r="AJ12">
         <v>0.2669963932089011</v>
       </c>
-      <c r="AI12">
+      <c r="AK12">
         <v>0.07839920617699385</v>
       </c>
-      <c r="AJ12">
+      <c r="AL12">
         <v>0.9092831096481332</v>
       </c>
-      <c r="AK12" t="s">
-        <v>81</v>
-      </c>
-      <c r="AL12">
+      <c r="AM12" t="s">
+        <v>126</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>143</v>
+      </c>
+      <c r="AO12">
         <v>0.005507852860808613</v>
       </c>
-      <c r="AM12">
+      <c r="AP12">
         <v>0.06609423432970336</v>
       </c>
-      <c r="AN12">
-        <v>12</v>
-      </c>
-      <c r="AO12">
+      <c r="AQ12">
+        <v>12</v>
+      </c>
+      <c r="AR12">
         <v>188804</v>
       </c>
-      <c r="AP12" t="s">
-        <v>47</v>
-      </c>
-      <c r="AQ12" t="s">
-        <v>50</v>
-      </c>
-      <c r="AR12" t="s">
-        <v>51</v>
-      </c>
       <c r="AS12" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="AT12" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="AU12" t="s">
-        <v>19</v>
-      </c>
-      <c r="AV12">
+        <v>76</v>
+      </c>
+      <c r="AV12" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW12" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX12" t="s">
+        <v>20</v>
+      </c>
+      <c r="AY12">
         <v>-1.990152824759337</v>
       </c>
-      <c r="AW12">
+      <c r="AZ12">
         <v>0.136674536596235</v>
       </c>
-      <c r="AX12">
+      <c r="BA12">
         <v>0.04268376633549423</v>
       </c>
-      <c r="AY12">
+      <c r="BB12">
         <v>0.4376354421718882</v>
       </c>
-      <c r="AZ12" t="s">
-        <v>94</v>
-      </c>
-      <c r="BA12">
+      <c r="BC12" t="s">
+        <v>158</v>
+      </c>
+      <c r="BD12" t="s">
+        <v>174</v>
+      </c>
+      <c r="BE12">
         <v>1.058566992823939E-05</v>
       </c>
-      <c r="BB12">
+      <c r="BF12">
         <v>0.0001270280391388726</v>
       </c>
-      <c r="BC12">
-        <v>12</v>
-      </c>
-      <c r="BD12">
+      <c r="BG12">
+        <v>12</v>
+      </c>
+      <c r="BH12">
         <v>196722</v>
       </c>
-      <c r="BE12" t="s">
-        <v>47</v>
-      </c>
-      <c r="BF12" t="s">
-        <v>50</v>
-      </c>
-      <c r="BG12" t="s">
-        <v>51</v>
-      </c>
-      <c r="BH12" t="s">
-        <v>53</v>
-      </c>
       <c r="BI12" t="s">
-        <v>59</v>
+        <v>72</v>
+      </c>
+      <c r="BJ12" t="s">
+        <v>75</v>
+      </c>
+      <c r="BK12" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL12" t="s">
+        <v>78</v>
+      </c>
+      <c r="BM12" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:61">
+    <row r="13" spans="1:65">
       <c r="A13" s="1">
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>0.3522763813132894</v>
@@ -3005,177 +3378,189 @@
         <v>1.500271748728031</v>
       </c>
       <c r="G13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13">
+        <v>32</v>
+      </c>
+      <c r="H13" t="s">
+        <v>56</v>
+      </c>
+      <c r="I13">
         <v>7.913251715683308E-65</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>9.49590205881997E-64</v>
       </c>
-      <c r="J13">
-        <v>12</v>
-      </c>
       <c r="K13">
+        <v>12</v>
+      </c>
+      <c r="L13">
         <v>188699</v>
       </c>
-      <c r="L13" t="s">
-        <v>47</v>
-      </c>
       <c r="M13" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="N13" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="O13" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="P13" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="Q13" t="s">
-        <v>20</v>
-      </c>
-      <c r="R13">
+        <v>84</v>
+      </c>
+      <c r="R13" t="s">
+        <v>21</v>
+      </c>
+      <c r="S13">
         <v>0.3406957468336467</v>
       </c>
-      <c r="S13">
+      <c r="T13">
         <v>1.405925418522077</v>
       </c>
-      <c r="T13">
+      <c r="U13">
         <v>1.331159965940817</v>
       </c>
-      <c r="U13">
+      <c r="V13">
         <v>1.484890120662145</v>
       </c>
-      <c r="V13" t="s">
-        <v>67</v>
-      </c>
-      <c r="W13">
+      <c r="W13" t="s">
+        <v>92</v>
+      </c>
+      <c r="X13" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y13">
         <v>4.901663425279109E-58</v>
       </c>
-      <c r="X13">
+      <c r="Z13">
         <v>5.881996110334931E-57</v>
       </c>
-      <c r="Y13">
-        <v>12</v>
-      </c>
-      <c r="Z13">
+      <c r="AA13">
+        <v>12</v>
+      </c>
+      <c r="AB13">
         <v>180261</v>
       </c>
-      <c r="AA13" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>50</v>
-      </c>
       <c r="AC13" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="AD13" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="AE13" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="AF13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG13">
+        <v>78</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI13">
         <v>0.3520782847540908</v>
       </c>
-      <c r="AH13">
+      <c r="AJ13">
         <v>1.422019841834895</v>
       </c>
-      <c r="AI13">
+      <c r="AK13">
         <v>1.34810446837541</v>
       </c>
-      <c r="AJ13">
+      <c r="AL13">
         <v>1.49998792972551</v>
       </c>
-      <c r="AK13" t="s">
-        <v>31</v>
-      </c>
-      <c r="AL13">
+      <c r="AM13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>144</v>
+      </c>
+      <c r="AO13">
         <v>9.775843964058E-65</v>
       </c>
-      <c r="AM13">
+      <c r="AP13">
         <v>1.17310127568696E-63</v>
       </c>
-      <c r="AN13">
-        <v>12</v>
-      </c>
-      <c r="AO13">
+      <c r="AQ13">
+        <v>12</v>
+      </c>
+      <c r="AR13">
         <v>188804</v>
       </c>
-      <c r="AP13" t="s">
-        <v>47</v>
-      </c>
-      <c r="AQ13" t="s">
-        <v>50</v>
-      </c>
-      <c r="AR13" t="s">
-        <v>51</v>
-      </c>
       <c r="AS13" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="AT13" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="AU13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AV13">
+        <v>76</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY13">
         <v>0.3405497075551718</v>
       </c>
-      <c r="AW13">
+      <c r="AZ13">
         <v>1.405720113180053</v>
       </c>
-      <c r="AX13">
+      <c r="BA13">
         <v>1.334134951730596</v>
       </c>
-      <c r="AY13">
+      <c r="BB13">
         <v>1.48114629186176</v>
       </c>
-      <c r="AZ13" t="s">
-        <v>67</v>
-      </c>
-      <c r="BA13">
+      <c r="BC13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD13" t="s">
+        <v>175</v>
+      </c>
+      <c r="BE13">
         <v>3.24206699683239E-63</v>
       </c>
-      <c r="BB13">
+      <c r="BF13">
         <v>3.890480396198868E-62</v>
       </c>
-      <c r="BC13">
-        <v>12</v>
-      </c>
-      <c r="BD13">
+      <c r="BG13">
+        <v>12</v>
+      </c>
+      <c r="BH13">
         <v>196722</v>
       </c>
-      <c r="BE13" t="s">
-        <v>47</v>
-      </c>
-      <c r="BF13" t="s">
-        <v>50</v>
-      </c>
-      <c r="BG13" t="s">
-        <v>51</v>
-      </c>
-      <c r="BH13" t="s">
-        <v>53</v>
-      </c>
       <c r="BI13" t="s">
-        <v>59</v>
+        <v>72</v>
+      </c>
+      <c r="BJ13" t="s">
+        <v>75</v>
+      </c>
+      <c r="BK13" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL13" t="s">
+        <v>78</v>
+      </c>
+      <c r="BM13" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:61">
+    <row r="14" spans="1:65">
       <c r="A14" s="1">
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14">
         <v>-0.1790764427892604</v>
@@ -3190,177 +3575,189 @@
         <v>2.092660809954686</v>
       </c>
       <c r="G14" t="s">
-        <v>32</v>
-      </c>
-      <c r="H14">
+        <v>33</v>
+      </c>
+      <c r="H14" t="s">
+        <v>57</v>
+      </c>
+      <c r="I14">
         <v>0.6151471159023996</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>7.381765390828795</v>
       </c>
-      <c r="J14">
-        <v>12</v>
-      </c>
       <c r="K14">
+        <v>12</v>
+      </c>
+      <c r="L14">
         <v>190286</v>
       </c>
-      <c r="L14" t="s">
-        <v>48</v>
-      </c>
       <c r="M14" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="N14" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="O14" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="P14" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="Q14" t="s">
-        <v>19</v>
-      </c>
-      <c r="R14">
+        <v>83</v>
+      </c>
+      <c r="R14" t="s">
+        <v>20</v>
+      </c>
+      <c r="S14">
         <v>0.005824697327685899</v>
       </c>
-      <c r="S14">
+      <c r="T14">
         <v>1.005841693861029</v>
       </c>
-      <c r="T14">
+      <c r="U14">
         <v>0.8635795029272267</v>
       </c>
-      <c r="U14">
+      <c r="V14">
         <v>1.171539516257463</v>
       </c>
-      <c r="V14" t="s">
-        <v>68</v>
-      </c>
-      <c r="W14">
+      <c r="W14" t="s">
+        <v>93</v>
+      </c>
+      <c r="X14" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y14">
         <v>0.9216250092625665</v>
       </c>
-      <c r="X14">
+      <c r="Z14">
         <v>11.0595001111508</v>
       </c>
-      <c r="Y14">
-        <v>12</v>
-      </c>
-      <c r="Z14">
+      <c r="AA14">
+        <v>12</v>
+      </c>
+      <c r="AB14">
         <v>181786</v>
       </c>
-      <c r="AA14" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>50</v>
-      </c>
       <c r="AC14" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="AD14" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="AE14" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="AF14" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG14">
+        <v>79</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI14">
         <v>-0.228326139766074</v>
       </c>
-      <c r="AH14">
+      <c r="AJ14">
         <v>0.7958646543917156</v>
       </c>
-      <c r="AI14">
+      <c r="AK14">
         <v>0.3703634130699436</v>
       </c>
-      <c r="AJ14">
+      <c r="AL14">
         <v>1.710213605765714</v>
       </c>
-      <c r="AK14" t="s">
-        <v>82</v>
-      </c>
-      <c r="AL14">
+      <c r="AM14" t="s">
+        <v>127</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>145</v>
+      </c>
+      <c r="AO14">
         <v>0.4419810852787366</v>
       </c>
-      <c r="AM14">
+      <c r="AP14">
         <v>5.303773023344839</v>
       </c>
-      <c r="AN14">
-        <v>12</v>
-      </c>
-      <c r="AO14">
+      <c r="AQ14">
+        <v>12</v>
+      </c>
+      <c r="AR14">
         <v>190396</v>
       </c>
-      <c r="AP14" t="s">
-        <v>48</v>
-      </c>
-      <c r="AQ14" t="s">
-        <v>50</v>
-      </c>
-      <c r="AR14" t="s">
-        <v>51</v>
-      </c>
       <c r="AS14" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="AT14" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="AU14" t="s">
-        <v>19</v>
-      </c>
-      <c r="AV14">
+        <v>76</v>
+      </c>
+      <c r="AV14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW14" t="s">
+        <v>83</v>
+      </c>
+      <c r="AX14" t="s">
+        <v>20</v>
+      </c>
+      <c r="AY14">
         <v>0.04888477731303434</v>
       </c>
-      <c r="AW14">
+      <c r="AZ14">
         <v>1.050099348500545</v>
       </c>
-      <c r="AX14">
+      <c r="BA14">
         <v>0.5151319330434712</v>
       </c>
-      <c r="AY14">
+      <c r="BB14">
         <v>2.14063343968275</v>
       </c>
-      <c r="AZ14" t="s">
-        <v>95</v>
-      </c>
-      <c r="BA14">
+      <c r="BC14" t="s">
+        <v>159</v>
+      </c>
+      <c r="BD14" t="s">
+        <v>176</v>
+      </c>
+      <c r="BE14">
         <v>0.8596667299092638</v>
       </c>
-      <c r="BB14">
+      <c r="BF14">
         <v>10.31600075891117</v>
       </c>
-      <c r="BC14">
-        <v>12</v>
-      </c>
-      <c r="BD14">
+      <c r="BG14">
+        <v>12</v>
+      </c>
+      <c r="BH14">
         <v>198382</v>
       </c>
-      <c r="BE14" t="s">
-        <v>48</v>
-      </c>
-      <c r="BF14" t="s">
-        <v>50</v>
-      </c>
-      <c r="BG14" t="s">
-        <v>51</v>
-      </c>
-      <c r="BH14" t="s">
-        <v>54</v>
-      </c>
       <c r="BI14" t="s">
-        <v>58</v>
+        <v>73</v>
+      </c>
+      <c r="BJ14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BK14" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BM14" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:61">
+    <row r="15" spans="1:65">
       <c r="A15" s="1">
         <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15">
         <v>-0.04786747989231508</v>
@@ -3375,177 +3772,189 @@
         <v>0.9847033312595347</v>
       </c>
       <c r="G15" t="s">
-        <v>33</v>
-      </c>
-      <c r="H15">
+        <v>34</v>
+      </c>
+      <c r="H15" t="s">
+        <v>58</v>
+      </c>
+      <c r="I15">
         <v>0.0001450827090919315</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>0.001740992509103177</v>
       </c>
-      <c r="J15">
-        <v>12</v>
-      </c>
       <c r="K15">
+        <v>12</v>
+      </c>
+      <c r="L15">
         <v>190286</v>
       </c>
-      <c r="L15" t="s">
-        <v>48</v>
-      </c>
       <c r="M15" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="N15" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="O15" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="P15" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="Q15" t="s">
-        <v>20</v>
-      </c>
-      <c r="R15">
+        <v>83</v>
+      </c>
+      <c r="R15" t="s">
+        <v>21</v>
+      </c>
+      <c r="S15">
         <v>-0.04800456130327536</v>
       </c>
-      <c r="S15">
+      <c r="T15">
         <v>0.9531294395551551</v>
       </c>
-      <c r="T15">
+      <c r="U15">
         <v>0.9219755549948806</v>
       </c>
-      <c r="U15">
+      <c r="V15">
         <v>0.9853360250443607</v>
       </c>
-      <c r="V15" t="s">
-        <v>33</v>
-      </c>
-      <c r="W15">
+      <c r="W15" t="s">
+        <v>34</v>
+      </c>
+      <c r="X15" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y15">
         <v>0.0001985476592649269</v>
       </c>
-      <c r="X15">
+      <c r="Z15">
         <v>0.002382571911179123</v>
       </c>
-      <c r="Y15">
-        <v>12</v>
-      </c>
-      <c r="Z15">
+      <c r="AA15">
+        <v>12</v>
+      </c>
+      <c r="AB15">
         <v>181786</v>
       </c>
-      <c r="AA15" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB15" t="s">
-        <v>50</v>
-      </c>
       <c r="AC15" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="AD15" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="AE15" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="AF15" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG15">
+        <v>79</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI15">
         <v>-0.04544204050662298</v>
       </c>
-      <c r="AH15">
+      <c r="AJ15">
         <v>0.9555749856090022</v>
       </c>
-      <c r="AI15">
+      <c r="AK15">
         <v>0.9250165108781125</v>
       </c>
-      <c r="AJ15">
+      <c r="AL15">
         <v>0.9871429778640624</v>
       </c>
-      <c r="AK15" t="s">
+      <c r="AM15" t="s">
+        <v>128</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>146</v>
+      </c>
+      <c r="AO15">
+        <v>0.0003165272075512534</v>
+      </c>
+      <c r="AP15">
+        <v>0.003798326490615041</v>
+      </c>
+      <c r="AQ15">
+        <v>12</v>
+      </c>
+      <c r="AR15">
+        <v>190396</v>
+      </c>
+      <c r="AS15" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT15" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU15" t="s">
+        <v>76</v>
+      </c>
+      <c r="AV15" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW15" t="s">
         <v>83</v>
       </c>
-      <c r="AL15">
-        <v>0.0003165272075512534</v>
-      </c>
-      <c r="AM15">
-        <v>0.003798326490615041</v>
-      </c>
-      <c r="AN15">
-        <v>12</v>
-      </c>
-      <c r="AO15">
-        <v>190396</v>
-      </c>
-      <c r="AP15" t="s">
-        <v>48</v>
-      </c>
-      <c r="AQ15" t="s">
-        <v>50</v>
-      </c>
-      <c r="AR15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AS15" t="s">
-        <v>54</v>
-      </c>
-      <c r="AT15" t="s">
-        <v>58</v>
-      </c>
-      <c r="AU15" t="s">
-        <v>20</v>
-      </c>
-      <c r="AV15">
+      <c r="AX15" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY15">
         <v>-0.0471868046718976</v>
       </c>
-      <c r="AW15">
+      <c r="AZ15">
         <v>0.953909186252976</v>
       </c>
-      <c r="AX15">
+      <c r="BA15">
         <v>0.9240509308427878</v>
       </c>
-      <c r="AY15">
+      <c r="BB15">
         <v>0.9847322320079205</v>
       </c>
-      <c r="AZ15" t="s">
-        <v>45</v>
-      </c>
-      <c r="BA15">
+      <c r="BC15" t="s">
+        <v>46</v>
+      </c>
+      <c r="BD15" t="s">
+        <v>153</v>
+      </c>
+      <c r="BE15">
         <v>0.000132362784871304</v>
       </c>
-      <c r="BB15">
+      <c r="BF15">
         <v>0.001588353418455648</v>
       </c>
-      <c r="BC15">
-        <v>12</v>
-      </c>
-      <c r="BD15">
+      <c r="BG15">
+        <v>12</v>
+      </c>
+      <c r="BH15">
         <v>198382</v>
       </c>
-      <c r="BE15" t="s">
-        <v>48</v>
-      </c>
-      <c r="BF15" t="s">
-        <v>50</v>
-      </c>
-      <c r="BG15" t="s">
-        <v>51</v>
-      </c>
-      <c r="BH15" t="s">
-        <v>54</v>
-      </c>
       <c r="BI15" t="s">
-        <v>58</v>
+        <v>73</v>
+      </c>
+      <c r="BJ15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BK15" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL15" t="s">
+        <v>79</v>
+      </c>
+      <c r="BM15" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="16" spans="1:61">
+    <row r="16" spans="1:65">
       <c r="A16" s="1">
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16">
         <v>1.181887380961214</v>
@@ -3560,177 +3969,189 @@
         <v>4.568995868128286</v>
       </c>
       <c r="G16" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16">
+        <v>35</v>
+      </c>
+      <c r="H16" t="s">
+        <v>59</v>
+      </c>
+      <c r="I16">
         <v>1.833788358566018E-19</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>2.200546030279222E-18</v>
       </c>
-      <c r="J16">
-        <v>12</v>
-      </c>
       <c r="K16">
+        <v>12</v>
+      </c>
+      <c r="L16">
         <v>172824</v>
       </c>
-      <c r="L16" t="s">
-        <v>46</v>
-      </c>
       <c r="M16" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="N16" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="O16" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="P16" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="Q16" t="s">
-        <v>21</v>
-      </c>
-      <c r="R16">
+        <v>83</v>
+      </c>
+      <c r="R16" t="s">
+        <v>22</v>
+      </c>
+      <c r="S16">
         <v>0.3218256056450025</v>
       </c>
-      <c r="S16">
+      <c r="T16">
         <v>1.37964415282404</v>
       </c>
-      <c r="T16">
+      <c r="U16">
         <v>1.256873659157324</v>
       </c>
-      <c r="U16">
+      <c r="V16">
         <v>1.51440677792366</v>
       </c>
-      <c r="V16" t="s">
-        <v>69</v>
-      </c>
-      <c r="W16">
+      <c r="W16" t="s">
+        <v>94</v>
+      </c>
+      <c r="X16" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y16">
         <v>5.858934121726623E-19</v>
       </c>
-      <c r="X16">
+      <c r="Z16">
         <v>7.030720946071947E-18</v>
       </c>
-      <c r="Y16">
-        <v>12</v>
-      </c>
-      <c r="Z16">
+      <c r="AA16">
+        <v>12</v>
+      </c>
+      <c r="AB16">
         <v>172872</v>
       </c>
-      <c r="AA16" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>49</v>
-      </c>
       <c r="AC16" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="AD16" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="AE16" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="AF16" t="s">
-        <v>21</v>
-      </c>
-      <c r="AG16">
+        <v>80</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI16">
         <v>1.047285447536786</v>
       </c>
-      <c r="AH16">
+      <c r="AJ16">
         <v>2.849904393383901</v>
       </c>
-      <c r="AI16">
+      <c r="AK16">
         <v>2.08704266950316</v>
       </c>
-      <c r="AJ16">
+      <c r="AL16">
         <v>3.891609486528787</v>
       </c>
-      <c r="AK16" t="s">
-        <v>84</v>
-      </c>
-      <c r="AL16">
+      <c r="AM16" t="s">
+        <v>129</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>147</v>
+      </c>
+      <c r="AO16">
         <v>4.75566911948853E-18</v>
       </c>
-      <c r="AM16">
+      <c r="AP16">
         <v>5.706802943386235E-17</v>
       </c>
-      <c r="AN16">
-        <v>12</v>
-      </c>
-      <c r="AO16">
+      <c r="AQ16">
+        <v>12</v>
+      </c>
+      <c r="AR16">
         <v>172836</v>
       </c>
-      <c r="AP16" t="s">
-        <v>46</v>
-      </c>
-      <c r="AQ16" t="s">
-        <v>49</v>
-      </c>
-      <c r="AR16" t="s">
-        <v>51</v>
-      </c>
       <c r="AS16" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="AT16" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="AU16" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV16">
+        <v>76</v>
+      </c>
+      <c r="AV16" t="s">
+        <v>80</v>
+      </c>
+      <c r="AW16" t="s">
+        <v>83</v>
+      </c>
+      <c r="AX16" t="s">
+        <v>22</v>
+      </c>
+      <c r="AY16">
         <v>1.071126816135797</v>
       </c>
-      <c r="AW16">
+      <c r="AZ16">
         <v>2.918666448184892</v>
       </c>
-      <c r="AX16">
+      <c r="BA16">
         <v>2.162566888044982</v>
       </c>
-      <c r="AY16">
+      <c r="BB16">
         <v>3.939121551732104</v>
       </c>
-      <c r="AZ16" t="s">
-        <v>96</v>
-      </c>
-      <c r="BA16">
+      <c r="BC16" t="s">
+        <v>160</v>
+      </c>
+      <c r="BD16" t="s">
+        <v>177</v>
+      </c>
+      <c r="BE16">
         <v>3.513956689640149E-20</v>
       </c>
-      <c r="BB16">
+      <c r="BF16">
         <v>4.216748027568179E-19</v>
       </c>
-      <c r="BC16">
-        <v>12</v>
-      </c>
-      <c r="BD16">
+      <c r="BG16">
+        <v>12</v>
+      </c>
+      <c r="BH16">
         <v>172815</v>
       </c>
-      <c r="BE16" t="s">
-        <v>46</v>
-      </c>
-      <c r="BF16" t="s">
-        <v>49</v>
-      </c>
-      <c r="BG16" t="s">
-        <v>51</v>
-      </c>
-      <c r="BH16" t="s">
-        <v>55</v>
-      </c>
       <c r="BI16" t="s">
-        <v>58</v>
+        <v>71</v>
+      </c>
+      <c r="BJ16" t="s">
+        <v>74</v>
+      </c>
+      <c r="BK16" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL16" t="s">
+        <v>80</v>
+      </c>
+      <c r="BM16" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:61">
+    <row r="17" spans="1:65">
       <c r="A17" s="1">
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17">
         <v>0.03209604274342277</v>
@@ -3745,177 +4166,189 @@
         <v>1.061472180948832</v>
       </c>
       <c r="G17" t="s">
-        <v>35</v>
-      </c>
-      <c r="H17">
+        <v>36</v>
+      </c>
+      <c r="H17" t="s">
+        <v>60</v>
+      </c>
+      <c r="I17">
         <v>0.002702475575087286</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>0.03242970690104743</v>
       </c>
-      <c r="J17">
-        <v>12</v>
-      </c>
       <c r="K17">
+        <v>12</v>
+      </c>
+      <c r="L17">
         <v>172824</v>
       </c>
-      <c r="L17" t="s">
-        <v>46</v>
-      </c>
       <c r="M17" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="N17" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="O17" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="P17" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="Q17" t="s">
-        <v>20</v>
-      </c>
-      <c r="R17">
+        <v>83</v>
+      </c>
+      <c r="R17" t="s">
+        <v>21</v>
+      </c>
+      <c r="S17">
         <v>0.03218582650469817</v>
       </c>
-      <c r="S17">
+      <c r="T17">
         <v>1.032709392252457</v>
       </c>
-      <c r="T17">
+      <c r="U17">
         <v>1.00463787072883</v>
       </c>
-      <c r="U17">
+      <c r="V17">
         <v>1.061565286278466</v>
       </c>
-      <c r="V17" t="s">
-        <v>35</v>
-      </c>
-      <c r="W17">
+      <c r="W17" t="s">
+        <v>36</v>
+      </c>
+      <c r="X17" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y17">
         <v>0.002627003145673741</v>
       </c>
-      <c r="X17">
+      <c r="Z17">
         <v>0.0315240377480849</v>
       </c>
-      <c r="Y17">
-        <v>12</v>
-      </c>
-      <c r="Z17">
+      <c r="AA17">
+        <v>12</v>
+      </c>
+      <c r="AB17">
         <v>172872</v>
       </c>
-      <c r="AA17" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB17" t="s">
-        <v>49</v>
-      </c>
       <c r="AC17" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="AD17" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="AE17" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="AF17" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG17">
+        <v>80</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI17">
         <v>0.03217297270625982</v>
       </c>
-      <c r="AH17">
+      <c r="AJ17">
         <v>1.032696118099395</v>
       </c>
-      <c r="AI17">
+      <c r="AK17">
         <v>1.004624312223959</v>
       </c>
-      <c r="AJ17">
+      <c r="AL17">
         <v>1.061552322954152</v>
       </c>
-      <c r="AK17" t="s">
-        <v>35</v>
-      </c>
-      <c r="AL17">
+      <c r="AM17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>113</v>
+      </c>
+      <c r="AO17">
         <v>0.00263801616466665</v>
       </c>
-      <c r="AM17">
+      <c r="AP17">
         <v>0.03165619397599979</v>
       </c>
-      <c r="AN17">
-        <v>12</v>
-      </c>
-      <c r="AO17">
+      <c r="AQ17">
+        <v>12</v>
+      </c>
+      <c r="AR17">
         <v>172836</v>
       </c>
-      <c r="AP17" t="s">
-        <v>46</v>
-      </c>
-      <c r="AQ17" t="s">
-        <v>49</v>
-      </c>
-      <c r="AR17" t="s">
-        <v>51</v>
-      </c>
       <c r="AS17" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="AT17" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="AU17" t="s">
-        <v>20</v>
-      </c>
-      <c r="AV17">
+        <v>76</v>
+      </c>
+      <c r="AV17" t="s">
+        <v>80</v>
+      </c>
+      <c r="AW17" t="s">
+        <v>83</v>
+      </c>
+      <c r="AX17" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY17">
         <v>0.0321729806151253</v>
       </c>
-      <c r="AW17">
+      <c r="AZ17">
         <v>1.03269612626685</v>
       </c>
-      <c r="AX17">
+      <c r="BA17">
         <v>1.004619526478088</v>
       </c>
-      <c r="AY17">
+      <c r="BB17">
         <v>1.061557396704472</v>
       </c>
-      <c r="AZ17" t="s">
-        <v>35</v>
-      </c>
-      <c r="BA17">
+      <c r="BC17" t="s">
+        <v>36</v>
+      </c>
+      <c r="BD17" t="s">
+        <v>113</v>
+      </c>
+      <c r="BE17">
         <v>0.002642530695018619</v>
       </c>
-      <c r="BB17">
+      <c r="BF17">
         <v>0.03171036834022343</v>
       </c>
-      <c r="BC17">
-        <v>12</v>
-      </c>
-      <c r="BD17">
+      <c r="BG17">
+        <v>12</v>
+      </c>
+      <c r="BH17">
         <v>172815</v>
       </c>
-      <c r="BE17" t="s">
-        <v>46</v>
-      </c>
-      <c r="BF17" t="s">
-        <v>49</v>
-      </c>
-      <c r="BG17" t="s">
-        <v>51</v>
-      </c>
-      <c r="BH17" t="s">
-        <v>55</v>
-      </c>
       <c r="BI17" t="s">
-        <v>58</v>
+        <v>71</v>
+      </c>
+      <c r="BJ17" t="s">
+        <v>74</v>
+      </c>
+      <c r="BK17" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL17" t="s">
+        <v>80</v>
+      </c>
+      <c r="BM17" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="18" spans="1:61">
+    <row r="18" spans="1:65">
       <c r="A18" s="1">
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18">
         <v>-3.015552014811446</v>
@@ -3930,177 +4363,189 @@
         <v>0.1036911364803779</v>
       </c>
       <c r="G18" t="s">
-        <v>36</v>
-      </c>
-      <c r="H18">
+        <v>37</v>
+      </c>
+      <c r="H18" t="s">
+        <v>61</v>
+      </c>
+      <c r="I18">
         <v>3.481460802653601E-25</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>4.177752963184322E-24</v>
       </c>
-      <c r="J18">
-        <v>12</v>
-      </c>
       <c r="K18">
+        <v>12</v>
+      </c>
+      <c r="L18">
         <v>172719</v>
       </c>
-      <c r="L18" t="s">
-        <v>47</v>
-      </c>
       <c r="M18" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="N18" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="O18" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="P18" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="Q18" t="s">
-        <v>21</v>
-      </c>
-      <c r="R18">
+        <v>84</v>
+      </c>
+      <c r="R18" t="s">
+        <v>22</v>
+      </c>
+      <c r="S18">
         <v>-0.9264686362233081</v>
       </c>
-      <c r="S18">
+      <c r="T18">
         <v>0.3959494860977817</v>
       </c>
-      <c r="T18">
+      <c r="U18">
         <v>0.3232695400068869</v>
       </c>
-      <c r="U18">
+      <c r="V18">
         <v>0.4849698970640955</v>
       </c>
-      <c r="V18" t="s">
-        <v>70</v>
-      </c>
-      <c r="W18">
+      <c r="W18" t="s">
+        <v>95</v>
+      </c>
+      <c r="X18" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y18">
         <v>5.748781512852104E-32</v>
       </c>
-      <c r="X18">
+      <c r="Z18">
         <v>6.898537815422524E-31</v>
       </c>
-      <c r="Y18">
-        <v>12</v>
-      </c>
-      <c r="Z18">
+      <c r="AA18">
+        <v>12</v>
+      </c>
+      <c r="AB18">
         <v>172767</v>
       </c>
-      <c r="AA18" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB18" t="s">
-        <v>49</v>
-      </c>
       <c r="AC18" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="AD18" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="AE18" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="AF18" t="s">
-        <v>21</v>
-      </c>
-      <c r="AG18">
+        <v>81</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI18">
         <v>-2.917809346440248</v>
       </c>
-      <c r="AH18">
+      <c r="AJ18">
         <v>0.05405196683186787</v>
       </c>
-      <c r="AI18">
+      <c r="AK18">
         <v>0.02736581058697646</v>
       </c>
-      <c r="AJ18">
+      <c r="AL18">
         <v>0.1067615048020451</v>
       </c>
-      <c r="AK18" t="s">
-        <v>85</v>
-      </c>
-      <c r="AL18">
+      <c r="AM18" t="s">
+        <v>130</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>148</v>
+      </c>
+      <c r="AO18">
         <v>2.395405852050432E-28</v>
       </c>
-      <c r="AM18">
+      <c r="AP18">
         <v>2.874487022460518E-27</v>
       </c>
-      <c r="AN18">
-        <v>12</v>
-      </c>
-      <c r="AO18">
+      <c r="AQ18">
+        <v>12</v>
+      </c>
+      <c r="AR18">
         <v>172731</v>
       </c>
-      <c r="AP18" t="s">
-        <v>47</v>
-      </c>
-      <c r="AQ18" t="s">
-        <v>49</v>
-      </c>
-      <c r="AR18" t="s">
-        <v>51</v>
-      </c>
       <c r="AS18" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="AT18" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="AU18" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV18">
+        <v>76</v>
+      </c>
+      <c r="AV18" t="s">
+        <v>81</v>
+      </c>
+      <c r="AW18" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX18" t="s">
+        <v>22</v>
+      </c>
+      <c r="AY18">
         <v>-3.096113379657473</v>
       </c>
-      <c r="AW18">
+      <c r="AZ18">
         <v>0.04522463223375382</v>
       </c>
-      <c r="AX18">
+      <c r="BA18">
         <v>0.02307214420039063</v>
       </c>
-      <c r="AY18">
+      <c r="BB18">
         <v>0.08864660964816855</v>
       </c>
-      <c r="AZ18" t="s">
-        <v>97</v>
-      </c>
-      <c r="BA18">
+      <c r="BC18" t="s">
+        <v>161</v>
+      </c>
+      <c r="BD18" t="s">
+        <v>178</v>
+      </c>
+      <c r="BE18">
         <v>2.158737397151926E-32</v>
       </c>
-      <c r="BB18">
+      <c r="BF18">
         <v>2.590484876582311E-31</v>
       </c>
-      <c r="BC18">
-        <v>12</v>
-      </c>
-      <c r="BD18">
+      <c r="BG18">
+        <v>12</v>
+      </c>
+      <c r="BH18">
         <v>172711</v>
       </c>
-      <c r="BE18" t="s">
-        <v>47</v>
-      </c>
-      <c r="BF18" t="s">
-        <v>49</v>
-      </c>
-      <c r="BG18" t="s">
-        <v>51</v>
-      </c>
-      <c r="BH18" t="s">
-        <v>56</v>
-      </c>
       <c r="BI18" t="s">
-        <v>59</v>
+        <v>72</v>
+      </c>
+      <c r="BJ18" t="s">
+        <v>74</v>
+      </c>
+      <c r="BK18" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL18" t="s">
+        <v>81</v>
+      </c>
+      <c r="BM18" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:61">
+    <row r="19" spans="1:65">
       <c r="A19" s="1">
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>0.4580052920479969</v>
@@ -4115,177 +4560,189 @@
         <v>1.672165691423796</v>
       </c>
       <c r="G19" t="s">
-        <v>37</v>
-      </c>
-      <c r="H19">
+        <v>38</v>
+      </c>
+      <c r="H19" t="s">
+        <v>62</v>
+      </c>
+      <c r="I19">
         <v>3.962264372069724E-98</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>4.754717246483669E-97</v>
       </c>
-      <c r="J19">
-        <v>12</v>
-      </c>
       <c r="K19">
+        <v>12</v>
+      </c>
+      <c r="L19">
         <v>172719</v>
       </c>
-      <c r="L19" t="s">
-        <v>47</v>
-      </c>
       <c r="M19" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="N19" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="O19" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="P19" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="Q19" t="s">
-        <v>20</v>
-      </c>
-      <c r="R19">
+        <v>84</v>
+      </c>
+      <c r="R19" t="s">
+        <v>21</v>
+      </c>
+      <c r="S19">
         <v>0.458251605632618</v>
       </c>
-      <c r="S19">
+      <c r="T19">
         <v>1.581306818715478</v>
       </c>
-      <c r="T19">
+      <c r="U19">
         <v>1.495034144204554</v>
       </c>
-      <c r="U19">
+      <c r="V19">
         <v>1.672557957695671</v>
       </c>
-      <c r="V19" t="s">
-        <v>37</v>
-      </c>
-      <c r="W19">
+      <c r="W19" t="s">
+        <v>38</v>
+      </c>
+      <c r="X19" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y19">
         <v>2.84503352584483E-98</v>
       </c>
-      <c r="X19">
+      <c r="Z19">
         <v>3.414040231013796E-97</v>
       </c>
-      <c r="Y19">
-        <v>12</v>
-      </c>
-      <c r="Z19">
+      <c r="AA19">
+        <v>12</v>
+      </c>
+      <c r="AB19">
         <v>172767</v>
       </c>
-      <c r="AA19" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB19" t="s">
-        <v>49</v>
-      </c>
       <c r="AC19" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="AD19" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="AE19" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="AF19" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG19">
+        <v>81</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI19">
         <v>0.4580641842753519</v>
       </c>
-      <c r="AH19">
+      <c r="AJ19">
         <v>1.581010475816621</v>
       </c>
-      <c r="AI19">
+      <c r="AK19">
         <v>1.494743711786982</v>
       </c>
-      <c r="AJ19">
+      <c r="AL19">
         <v>1.672255989392059</v>
       </c>
-      <c r="AK19" t="s">
-        <v>37</v>
-      </c>
-      <c r="AL19">
+      <c r="AM19" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>62</v>
+      </c>
+      <c r="AO19">
         <v>3.600976899059602E-98</v>
       </c>
-      <c r="AM19">
+      <c r="AP19">
         <v>4.321172278871522E-97</v>
       </c>
-      <c r="AN19">
-        <v>12</v>
-      </c>
-      <c r="AO19">
+      <c r="AQ19">
+        <v>12</v>
+      </c>
+      <c r="AR19">
         <v>172731</v>
       </c>
-      <c r="AP19" t="s">
-        <v>47</v>
-      </c>
-      <c r="AQ19" t="s">
-        <v>49</v>
-      </c>
-      <c r="AR19" t="s">
-        <v>51</v>
-      </c>
       <c r="AS19" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="AT19" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="AU19" t="s">
-        <v>20</v>
-      </c>
-      <c r="AV19">
+        <v>76</v>
+      </c>
+      <c r="AV19" t="s">
+        <v>81</v>
+      </c>
+      <c r="AW19" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX19" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY19">
         <v>0.4580680610921018</v>
       </c>
-      <c r="AW19">
+      <c r="AZ19">
         <v>1.581016605116397</v>
       </c>
-      <c r="AX19">
+      <c r="BA19">
         <v>1.494745552333732</v>
       </c>
-      <c r="AY19">
+      <c r="BB19">
         <v>1.672266896363166</v>
       </c>
-      <c r="AZ19" t="s">
-        <v>37</v>
-      </c>
-      <c r="BA19">
+      <c r="BC19" t="s">
+        <v>38</v>
+      </c>
+      <c r="BD19" t="s">
+        <v>62</v>
+      </c>
+      <c r="BE19">
         <v>3.663243263366753E-98</v>
       </c>
-      <c r="BB19">
+      <c r="BF19">
         <v>4.395891916040104E-97</v>
       </c>
-      <c r="BC19">
-        <v>12</v>
-      </c>
-      <c r="BD19">
+      <c r="BG19">
+        <v>12</v>
+      </c>
+      <c r="BH19">
         <v>172711</v>
       </c>
-      <c r="BE19" t="s">
-        <v>47</v>
-      </c>
-      <c r="BF19" t="s">
-        <v>49</v>
-      </c>
-      <c r="BG19" t="s">
-        <v>51</v>
-      </c>
-      <c r="BH19" t="s">
-        <v>56</v>
-      </c>
       <c r="BI19" t="s">
-        <v>59</v>
+        <v>72</v>
+      </c>
+      <c r="BJ19" t="s">
+        <v>74</v>
+      </c>
+      <c r="BK19" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL19" t="s">
+        <v>81</v>
+      </c>
+      <c r="BM19" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="20" spans="1:61">
+    <row r="20" spans="1:65">
       <c r="A20" s="1">
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>0.07940439647424492</v>
@@ -4300,177 +4757,189 @@
         <v>1.778044563505676</v>
       </c>
       <c r="G20" t="s">
-        <v>38</v>
-      </c>
-      <c r="H20">
+        <v>39</v>
+      </c>
+      <c r="H20" t="s">
+        <v>63</v>
+      </c>
+      <c r="I20">
         <v>0.680140083755336</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>8.161681005064032</v>
       </c>
-      <c r="J20">
-        <v>12</v>
-      </c>
       <c r="K20">
+        <v>12</v>
+      </c>
+      <c r="L20">
         <v>173819</v>
       </c>
-      <c r="L20" t="s">
-        <v>48</v>
-      </c>
       <c r="M20" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="N20" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="O20" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="P20" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="Q20" t="s">
-        <v>21</v>
-      </c>
-      <c r="R20">
+        <v>83</v>
+      </c>
+      <c r="R20" t="s">
+        <v>22</v>
+      </c>
+      <c r="S20">
         <v>-0.0007800590934148912</v>
       </c>
-      <c r="S20">
+      <c r="T20">
         <v>0.9992202450735852</v>
       </c>
-      <c r="T20">
+      <c r="U20">
         <v>0.8725342247582352</v>
       </c>
-      <c r="U20">
+      <c r="V20">
         <v>1.144300211767128</v>
       </c>
-      <c r="V20" t="s">
-        <v>71</v>
-      </c>
-      <c r="W20">
+      <c r="W20" t="s">
+        <v>96</v>
+      </c>
+      <c r="X20" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y20">
         <v>0.9881751824380927</v>
       </c>
-      <c r="X20">
+      <c r="Z20">
         <v>11.85810218925711</v>
       </c>
-      <c r="Y20">
-        <v>12</v>
-      </c>
-      <c r="Z20">
+      <c r="AA20">
+        <v>12</v>
+      </c>
+      <c r="AB20">
         <v>173867</v>
       </c>
-      <c r="AA20" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>49</v>
-      </c>
       <c r="AC20" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="AD20" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="AE20" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="AF20" t="s">
-        <v>21</v>
-      </c>
-      <c r="AG20">
+        <v>82</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI20">
         <v>0.1182586323590395</v>
       </c>
-      <c r="AH20">
+      <c r="AJ20">
         <v>1.125535173543787</v>
       </c>
-      <c r="AI20">
+      <c r="AK20">
         <v>0.7183168432095079</v>
       </c>
-      <c r="AJ20">
+      <c r="AL20">
         <v>1.763608133179681</v>
       </c>
-      <c r="AK20" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL20">
+      <c r="AM20" t="s">
+        <v>131</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>149</v>
+      </c>
+      <c r="AO20">
         <v>0.4975993102512232</v>
       </c>
-      <c r="AM20">
+      <c r="AP20">
         <v>5.971191723014678</v>
       </c>
-      <c r="AN20">
-        <v>12</v>
-      </c>
-      <c r="AO20">
+      <c r="AQ20">
+        <v>12</v>
+      </c>
+      <c r="AR20">
         <v>173831</v>
       </c>
-      <c r="AP20" t="s">
-        <v>48</v>
-      </c>
-      <c r="AQ20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AR20" t="s">
-        <v>51</v>
-      </c>
       <c r="AS20" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="AT20" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="AU20" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV20">
+        <v>76</v>
+      </c>
+      <c r="AV20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AW20" t="s">
+        <v>83</v>
+      </c>
+      <c r="AX20" t="s">
+        <v>22</v>
+      </c>
+      <c r="AY20">
         <v>-0.04091139849560724</v>
       </c>
-      <c r="AW20">
+      <c r="AZ20">
         <v>0.9599141760202217</v>
       </c>
-      <c r="AX20">
+      <c r="BA20">
         <v>0.6094696046630048</v>
       </c>
-      <c r="AY20">
+      <c r="BB20">
         <v>1.511864116396866</v>
       </c>
-      <c r="AZ20" t="s">
-        <v>98</v>
-      </c>
-      <c r="BA20">
+      <c r="BC20" t="s">
+        <v>162</v>
+      </c>
+      <c r="BD20" t="s">
+        <v>179</v>
+      </c>
+      <c r="BE20">
         <v>0.8165488455799234</v>
       </c>
-      <c r="BB20">
+      <c r="BF20">
         <v>9.79858614695908</v>
       </c>
-      <c r="BC20">
-        <v>12</v>
-      </c>
-      <c r="BD20">
+      <c r="BG20">
+        <v>12</v>
+      </c>
+      <c r="BH20">
         <v>173810</v>
       </c>
-      <c r="BE20" t="s">
-        <v>48</v>
-      </c>
-      <c r="BF20" t="s">
-        <v>49</v>
-      </c>
-      <c r="BG20" t="s">
-        <v>51</v>
-      </c>
-      <c r="BH20" t="s">
-        <v>57</v>
-      </c>
       <c r="BI20" t="s">
-        <v>58</v>
+        <v>73</v>
+      </c>
+      <c r="BJ20" t="s">
+        <v>74</v>
+      </c>
+      <c r="BK20" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL20" t="s">
+        <v>82</v>
+      </c>
+      <c r="BM20" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="21" spans="1:61">
+    <row r="21" spans="1:65">
       <c r="A21" s="1">
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C21">
         <v>-0.03433052753764375</v>
@@ -4485,177 +4954,189 @@
         <v>1.002919176363495</v>
       </c>
       <c r="G21" t="s">
-        <v>39</v>
-      </c>
-      <c r="H21">
+        <v>40</v>
+      </c>
+      <c r="H21" t="s">
+        <v>64</v>
+      </c>
+      <c r="I21">
         <v>0.01758519494059008</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>0.211022339287081</v>
       </c>
-      <c r="J21">
-        <v>12</v>
-      </c>
       <c r="K21">
+        <v>12</v>
+      </c>
+      <c r="L21">
         <v>173819</v>
       </c>
-      <c r="L21" t="s">
-        <v>48</v>
-      </c>
       <c r="M21" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="N21" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="O21" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="P21" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="Q21" t="s">
-        <v>20</v>
-      </c>
-      <c r="R21">
+        <v>83</v>
+      </c>
+      <c r="R21" t="s">
+        <v>21</v>
+      </c>
+      <c r="S21">
         <v>-0.03457022968276282</v>
       </c>
-      <c r="S21">
+      <c r="T21">
         <v>0.9660204939912933</v>
       </c>
-      <c r="T21">
+      <c r="U21">
         <v>0.930710049706409</v>
       </c>
-      <c r="U21">
+      <c r="V21">
         <v>1.002670590164528</v>
       </c>
-      <c r="V21" t="s">
-        <v>39</v>
-      </c>
-      <c r="W21">
+      <c r="W21" t="s">
+        <v>40</v>
+      </c>
+      <c r="X21" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y21">
         <v>0.01678692420191883</v>
       </c>
-      <c r="X21">
+      <c r="Z21">
         <v>0.2014430904230259</v>
       </c>
-      <c r="Y21">
-        <v>12</v>
-      </c>
-      <c r="Z21">
+      <c r="AA21">
+        <v>12</v>
+      </c>
+      <c r="AB21">
         <v>173867</v>
       </c>
-      <c r="AA21" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB21" t="s">
-        <v>49</v>
-      </c>
       <c r="AC21" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="AD21" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="AE21" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="AF21" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG21">
+        <v>82</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI21">
         <v>-0.03419796675221089</v>
       </c>
-      <c r="AH21">
+      <c r="AJ21">
         <v>0.9663801745550763</v>
       </c>
-      <c r="AI21">
+      <c r="AK21">
         <v>0.9310497176317183</v>
       </c>
-      <c r="AJ21">
+      <c r="AL21">
         <v>1.003051313036868</v>
       </c>
-      <c r="AK21" t="s">
-        <v>39</v>
-      </c>
-      <c r="AL21">
+      <c r="AM21" t="s">
+        <v>40</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO21">
         <v>0.01802410401585062</v>
       </c>
-      <c r="AM21">
+      <c r="AP21">
         <v>0.2162892481902075</v>
       </c>
-      <c r="AN21">
-        <v>12</v>
-      </c>
-      <c r="AO21">
+      <c r="AQ21">
+        <v>12</v>
+      </c>
+      <c r="AR21">
         <v>173831</v>
       </c>
-      <c r="AP21" t="s">
-        <v>48</v>
-      </c>
-      <c r="AQ21" t="s">
-        <v>49</v>
-      </c>
-      <c r="AR21" t="s">
-        <v>51</v>
-      </c>
       <c r="AS21" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="AT21" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="AU21" t="s">
-        <v>20</v>
-      </c>
-      <c r="AV21">
+        <v>76</v>
+      </c>
+      <c r="AV21" t="s">
+        <v>82</v>
+      </c>
+      <c r="AW21" t="s">
+        <v>83</v>
+      </c>
+      <c r="AX21" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY21">
         <v>-0.03457364814234975</v>
       </c>
-      <c r="AW21">
+      <c r="AZ21">
         <v>0.9660171916949188</v>
       </c>
-      <c r="AX21">
+      <c r="BA21">
         <v>0.9307026904731516</v>
       </c>
-      <c r="AY21">
+      <c r="BB21">
         <v>1.002671663252334</v>
       </c>
-      <c r="AZ21" t="s">
-        <v>39</v>
-      </c>
-      <c r="BA21">
+      <c r="BC21" t="s">
+        <v>40</v>
+      </c>
+      <c r="BD21" t="s">
+        <v>64</v>
+      </c>
+      <c r="BE21">
         <v>0.01678929243137744</v>
       </c>
-      <c r="BB21">
+      <c r="BF21">
         <v>0.2014715091765293</v>
       </c>
-      <c r="BC21">
-        <v>12</v>
-      </c>
-      <c r="BD21">
+      <c r="BG21">
+        <v>12</v>
+      </c>
+      <c r="BH21">
         <v>173810</v>
       </c>
-      <c r="BE21" t="s">
-        <v>48</v>
-      </c>
-      <c r="BF21" t="s">
-        <v>49</v>
-      </c>
-      <c r="BG21" t="s">
-        <v>51</v>
-      </c>
-      <c r="BH21" t="s">
-        <v>57</v>
-      </c>
       <c r="BI21" t="s">
-        <v>58</v>
+        <v>73</v>
+      </c>
+      <c r="BJ21" t="s">
+        <v>74</v>
+      </c>
+      <c r="BK21" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL21" t="s">
+        <v>82</v>
+      </c>
+      <c r="BM21" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="22" spans="1:61">
+    <row r="22" spans="1:65">
       <c r="A22" s="1">
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C22">
         <v>0.4133526451335411</v>
@@ -4670,177 +5151,189 @@
         <v>2.186047229880042</v>
       </c>
       <c r="G22" t="s">
-        <v>40</v>
-      </c>
-      <c r="H22">
+        <v>41</v>
+      </c>
+      <c r="H22" t="s">
+        <v>65</v>
+      </c>
+      <c r="I22">
         <v>0.003883757921750095</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>0.04660509506100114</v>
       </c>
-      <c r="J22">
-        <v>12</v>
-      </c>
       <c r="K22">
+        <v>12</v>
+      </c>
+      <c r="L22">
         <v>201858</v>
       </c>
-      <c r="L22" t="s">
-        <v>46</v>
-      </c>
       <c r="M22" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="N22" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="O22" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="P22" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="Q22" t="s">
-        <v>21</v>
-      </c>
-      <c r="R22">
+        <v>83</v>
+      </c>
+      <c r="R22" t="s">
+        <v>22</v>
+      </c>
+      <c r="S22">
         <v>0.1015076567050256</v>
       </c>
-      <c r="S22">
+      <c r="T22">
         <v>1.106838393094578</v>
       </c>
-      <c r="T22">
+      <c r="U22">
         <v>1.003611934473518</v>
       </c>
-      <c r="U22">
+      <c r="V22">
         <v>1.220682204293292</v>
       </c>
-      <c r="V22" t="s">
-        <v>72</v>
-      </c>
-      <c r="W22">
+      <c r="W22" t="s">
+        <v>97</v>
+      </c>
+      <c r="X22" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y22">
         <v>0.007569576924841752</v>
       </c>
-      <c r="X22">
+      <c r="Z22">
         <v>0.09083492309810101</v>
       </c>
-      <c r="Y22">
-        <v>12</v>
-      </c>
-      <c r="Z22">
+      <c r="AA22">
+        <v>12</v>
+      </c>
+      <c r="AB22">
         <v>201887</v>
       </c>
-      <c r="AA22" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB22" t="s">
-        <v>50</v>
-      </c>
       <c r="AC22" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="AD22" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AE22" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="AF22" t="s">
-        <v>21</v>
-      </c>
-      <c r="AG22">
+        <v>80</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI22">
         <v>0.3618302295150957</v>
       </c>
-      <c r="AH22">
+      <c r="AJ22">
         <v>1.435955138465461</v>
       </c>
-      <c r="AI22">
+      <c r="AK22">
         <v>1.033182287534628</v>
       </c>
-      <c r="AJ22">
+      <c r="AL22">
         <v>1.995743814584366</v>
       </c>
-      <c r="AK22" t="s">
-        <v>87</v>
-      </c>
-      <c r="AL22">
+      <c r="AM22" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN22" t="s">
+        <v>150</v>
+      </c>
+      <c r="AO22">
         <v>0.004636497898645121</v>
       </c>
-      <c r="AM22">
+      <c r="AP22">
         <v>0.05563797478374145</v>
       </c>
-      <c r="AN22">
-        <v>12</v>
-      </c>
-      <c r="AO22">
+      <c r="AQ22">
+        <v>12</v>
+      </c>
+      <c r="AR22">
         <v>201868</v>
       </c>
-      <c r="AP22" t="s">
-        <v>46</v>
-      </c>
-      <c r="AQ22" t="s">
-        <v>50</v>
-      </c>
-      <c r="AR22" t="s">
-        <v>51</v>
-      </c>
       <c r="AS22" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="AT22" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="AU22" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV22">
+        <v>76</v>
+      </c>
+      <c r="AV22" t="s">
+        <v>80</v>
+      </c>
+      <c r="AW22" t="s">
+        <v>83</v>
+      </c>
+      <c r="AX22" t="s">
+        <v>22</v>
+      </c>
+      <c r="AY22">
         <v>0.4262806306169947</v>
       </c>
-      <c r="AW22">
+      <c r="AZ22">
         <v>1.5315505147973</v>
       </c>
-      <c r="AX22">
+      <c r="BA22">
         <v>1.112658800666058</v>
       </c>
-      <c r="AY22">
+      <c r="BB22">
         <v>2.108145801724415</v>
       </c>
-      <c r="AZ22" t="s">
-        <v>99</v>
-      </c>
-      <c r="BA22">
+      <c r="BC22" t="s">
+        <v>163</v>
+      </c>
+      <c r="BD22" t="s">
+        <v>180</v>
+      </c>
+      <c r="BE22">
         <v>0.0005895029339672645</v>
       </c>
-      <c r="BB22">
+      <c r="BF22">
         <v>0.007074035207607174</v>
       </c>
-      <c r="BC22">
-        <v>12</v>
-      </c>
-      <c r="BD22">
+      <c r="BG22">
+        <v>12</v>
+      </c>
+      <c r="BH22">
         <v>201856</v>
       </c>
-      <c r="BE22" t="s">
-        <v>46</v>
-      </c>
-      <c r="BF22" t="s">
-        <v>50</v>
-      </c>
-      <c r="BG22" t="s">
-        <v>51</v>
-      </c>
-      <c r="BH22" t="s">
-        <v>55</v>
-      </c>
       <c r="BI22" t="s">
-        <v>58</v>
+        <v>71</v>
+      </c>
+      <c r="BJ22" t="s">
+        <v>75</v>
+      </c>
+      <c r="BK22" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL22" t="s">
+        <v>80</v>
+      </c>
+      <c r="BM22" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:61">
+    <row r="23" spans="1:65">
       <c r="A23" s="1">
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C23">
         <v>-0.07768833871503841</v>
@@ -4855,177 +5348,189 @@
         <v>0.950671506078812</v>
       </c>
       <c r="G23" t="s">
-        <v>41</v>
-      </c>
-      <c r="H23">
+        <v>42</v>
+      </c>
+      <c r="H23" t="s">
+        <v>66</v>
+      </c>
+      <c r="I23">
         <v>1.538862335337243E-13</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>1.846634802404691E-12</v>
       </c>
-      <c r="J23">
-        <v>12</v>
-      </c>
       <c r="K23">
+        <v>12</v>
+      </c>
+      <c r="L23">
         <v>201858</v>
       </c>
-      <c r="L23" t="s">
-        <v>46</v>
-      </c>
       <c r="M23" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="N23" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="O23" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="P23" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="Q23" t="s">
-        <v>20</v>
-      </c>
-      <c r="R23">
+        <v>83</v>
+      </c>
+      <c r="R23" t="s">
+        <v>21</v>
+      </c>
+      <c r="S23">
         <v>-0.07774086727838896</v>
       </c>
-      <c r="S23">
+      <c r="T23">
         <v>0.9252041461510386</v>
       </c>
-      <c r="T23">
+      <c r="U23">
         <v>0.9004680137404376</v>
       </c>
-      <c r="U23">
+      <c r="V23">
         <v>0.950619787702773</v>
       </c>
-      <c r="V23" t="s">
-        <v>41</v>
-      </c>
-      <c r="W23">
+      <c r="W23" t="s">
+        <v>42</v>
+      </c>
+      <c r="X23" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y23">
         <v>1.476494246283972E-13</v>
       </c>
-      <c r="X23">
+      <c r="Z23">
         <v>1.771793095540766E-12</v>
       </c>
-      <c r="Y23">
-        <v>12</v>
-      </c>
-      <c r="Z23">
+      <c r="AA23">
+        <v>12</v>
+      </c>
+      <c r="AB23">
         <v>201887</v>
       </c>
-      <c r="AA23" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB23" t="s">
-        <v>50</v>
-      </c>
       <c r="AC23" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="AD23" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AE23" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="AF23" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG23">
+        <v>80</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI23">
         <v>-0.07762886026949971</v>
       </c>
-      <c r="AH23">
+      <c r="AJ23">
         <v>0.9253077813038844</v>
       </c>
-      <c r="AI23">
+      <c r="AK23">
         <v>0.9005672253435135</v>
       </c>
-      <c r="AJ23">
+      <c r="AL23">
         <v>0.9507280145742913</v>
       </c>
-      <c r="AK23" t="s">
-        <v>41</v>
-      </c>
-      <c r="AL23">
+      <c r="AM23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>66</v>
+      </c>
+      <c r="AO23">
         <v>1.605486933491994E-13</v>
       </c>
-      <c r="AM23">
+      <c r="AP23">
         <v>1.926584320190393E-12</v>
       </c>
-      <c r="AN23">
-        <v>12</v>
-      </c>
-      <c r="AO23">
+      <c r="AQ23">
+        <v>12</v>
+      </c>
+      <c r="AR23">
         <v>201868</v>
       </c>
-      <c r="AP23" t="s">
-        <v>46</v>
-      </c>
-      <c r="AQ23" t="s">
-        <v>50</v>
-      </c>
-      <c r="AR23" t="s">
-        <v>51</v>
-      </c>
       <c r="AS23" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="AT23" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="AU23" t="s">
-        <v>20</v>
-      </c>
-      <c r="AV23">
+        <v>76</v>
+      </c>
+      <c r="AV23" t="s">
+        <v>80</v>
+      </c>
+      <c r="AW23" t="s">
+        <v>83</v>
+      </c>
+      <c r="AX23" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY23">
         <v>-0.07743231984557075</v>
       </c>
-      <c r="AW23">
+      <c r="AZ23">
         <v>0.9254896595601159</v>
       </c>
-      <c r="AX23">
+      <c r="BA23">
         <v>0.9007427900475463</v>
       </c>
-      <c r="AY23">
+      <c r="BB23">
         <v>0.9509164207769975</v>
       </c>
-      <c r="AZ23" t="s">
-        <v>41</v>
-      </c>
-      <c r="BA23">
+      <c r="BC23" t="s">
+        <v>42</v>
+      </c>
+      <c r="BD23" t="s">
+        <v>66</v>
+      </c>
+      <c r="BE23">
         <v>1.852988070368048E-13</v>
       </c>
-      <c r="BB23">
+      <c r="BF23">
         <v>2.223585684441658E-12</v>
       </c>
-      <c r="BC23">
-        <v>12</v>
-      </c>
-      <c r="BD23">
+      <c r="BG23">
+        <v>12</v>
+      </c>
+      <c r="BH23">
         <v>201856</v>
       </c>
-      <c r="BE23" t="s">
-        <v>46</v>
-      </c>
-      <c r="BF23" t="s">
-        <v>50</v>
-      </c>
-      <c r="BG23" t="s">
-        <v>51</v>
-      </c>
-      <c r="BH23" t="s">
-        <v>55</v>
-      </c>
       <c r="BI23" t="s">
-        <v>58</v>
+        <v>71</v>
+      </c>
+      <c r="BJ23" t="s">
+        <v>75</v>
+      </c>
+      <c r="BK23" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL23" t="s">
+        <v>80</v>
+      </c>
+      <c r="BM23" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:61">
+    <row r="24" spans="1:65">
       <c r="A24" s="1">
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C24">
         <v>-2.904967408844841</v>
@@ -5040,177 +5545,189 @@
         <v>0.1126991603549672</v>
       </c>
       <c r="G24" t="s">
-        <v>42</v>
-      </c>
-      <c r="H24">
+        <v>43</v>
+      </c>
+      <c r="H24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I24">
         <v>3.585200581856068E-25</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>4.302240698227281E-24</v>
       </c>
-      <c r="J24">
-        <v>12</v>
-      </c>
       <c r="K24">
+        <v>12</v>
+      </c>
+      <c r="L24">
         <v>200241</v>
       </c>
-      <c r="L24" t="s">
-        <v>47</v>
-      </c>
       <c r="M24" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="N24" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="O24" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="P24" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="Q24" t="s">
-        <v>21</v>
-      </c>
-      <c r="R24">
+        <v>84</v>
+      </c>
+      <c r="R24" t="s">
+        <v>22</v>
+      </c>
+      <c r="S24">
         <v>-0.7837884718224358</v>
       </c>
-      <c r="S24">
+      <c r="T24">
         <v>0.4566726385382894</v>
       </c>
-      <c r="T24">
+      <c r="U24">
         <v>0.3779226331257006</v>
       </c>
-      <c r="U24">
+      <c r="V24">
         <v>0.551832254831262</v>
       </c>
-      <c r="V24" t="s">
-        <v>73</v>
-      </c>
-      <c r="W24">
+      <c r="W24" t="s">
+        <v>98</v>
+      </c>
+      <c r="X24" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y24">
         <v>1.461986316586652E-26</v>
       </c>
-      <c r="X24">
+      <c r="Z24">
         <v>1.754383579903982E-25</v>
       </c>
-      <c r="Y24">
-        <v>12</v>
-      </c>
-      <c r="Z24">
+      <c r="AA24">
+        <v>12</v>
+      </c>
+      <c r="AB24">
         <v>200269</v>
       </c>
-      <c r="AA24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB24" t="s">
-        <v>50</v>
-      </c>
       <c r="AC24" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="AD24" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="AE24" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="AF24" t="s">
-        <v>21</v>
-      </c>
-      <c r="AG24">
+        <v>81</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI24">
         <v>-2.351490324299165</v>
       </c>
-      <c r="AH24">
+      <c r="AJ24">
         <v>0.09522713709374112</v>
       </c>
-      <c r="AI24">
+      <c r="AK24">
         <v>0.05028147088435017</v>
       </c>
-      <c r="AJ24">
+      <c r="AL24">
         <v>0.1803488935303322</v>
       </c>
-      <c r="AK24" t="s">
-        <v>88</v>
-      </c>
-      <c r="AL24">
+      <c r="AM24" t="s">
+        <v>133</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>151</v>
+      </c>
+      <c r="AO24">
         <v>2.436670496434098E-21</v>
       </c>
-      <c r="AM24">
+      <c r="AP24">
         <v>2.924004595720918E-20</v>
       </c>
-      <c r="AN24">
-        <v>12</v>
-      </c>
-      <c r="AO24">
+      <c r="AQ24">
+        <v>12</v>
+      </c>
+      <c r="AR24">
         <v>200251</v>
       </c>
-      <c r="AP24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AQ24" t="s">
-        <v>50</v>
-      </c>
-      <c r="AR24" t="s">
-        <v>51</v>
-      </c>
       <c r="AS24" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="AT24" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="AU24" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV24">
+        <v>76</v>
+      </c>
+      <c r="AV24" t="s">
+        <v>81</v>
+      </c>
+      <c r="AW24" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX24" t="s">
+        <v>22</v>
+      </c>
+      <c r="AY24">
         <v>-2.642308652372884</v>
       </c>
-      <c r="AW24">
+      <c r="AZ24">
         <v>0.07119671121918017</v>
       </c>
-      <c r="AX24">
+      <c r="BA24">
         <v>0.0378106847233592</v>
       </c>
-      <c r="AY24">
+      <c r="BB24">
         <v>0.1340618855626213</v>
       </c>
-      <c r="AZ24" t="s">
-        <v>100</v>
-      </c>
-      <c r="BA24">
+      <c r="BC24" t="s">
+        <v>164</v>
+      </c>
+      <c r="BD24" t="s">
+        <v>181</v>
+      </c>
+      <c r="BE24">
         <v>5.634451422127399E-27</v>
       </c>
-      <c r="BB24">
+      <c r="BF24">
         <v>6.761341706552879E-26</v>
       </c>
-      <c r="BC24">
-        <v>12</v>
-      </c>
-      <c r="BD24">
+      <c r="BG24">
+        <v>12</v>
+      </c>
+      <c r="BH24">
         <v>200238</v>
       </c>
-      <c r="BE24" t="s">
-        <v>47</v>
-      </c>
-      <c r="BF24" t="s">
-        <v>50</v>
-      </c>
-      <c r="BG24" t="s">
-        <v>51</v>
-      </c>
-      <c r="BH24" t="s">
-        <v>56</v>
-      </c>
       <c r="BI24" t="s">
-        <v>59</v>
+        <v>72</v>
+      </c>
+      <c r="BJ24" t="s">
+        <v>75</v>
+      </c>
+      <c r="BK24" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL24" t="s">
+        <v>81</v>
+      </c>
+      <c r="BM24" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:61">
+    <row r="25" spans="1:65">
       <c r="A25" s="1">
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C25">
         <v>0.3422180089579703</v>
@@ -5225,177 +5742,189 @@
         <v>1.48291330433717</v>
       </c>
       <c r="G25" t="s">
-        <v>43</v>
-      </c>
-      <c r="H25">
+        <v>44</v>
+      </c>
+      <c r="H25" t="s">
+        <v>68</v>
+      </c>
+      <c r="I25">
         <v>5.800059320809429E-65</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>6.960071184971315E-64</v>
       </c>
-      <c r="J25">
-        <v>12</v>
-      </c>
       <c r="K25">
+        <v>12</v>
+      </c>
+      <c r="L25">
         <v>200241</v>
       </c>
-      <c r="L25" t="s">
-        <v>47</v>
-      </c>
       <c r="M25" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="N25" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="O25" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="P25" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="Q25" t="s">
-        <v>20</v>
-      </c>
-      <c r="R25">
+        <v>84</v>
+      </c>
+      <c r="R25" t="s">
+        <v>21</v>
+      </c>
+      <c r="S25">
         <v>0.3418360598856223</v>
       </c>
-      <c r="S25">
+      <c r="T25">
         <v>1.407529528046615</v>
       </c>
-      <c r="T25">
+      <c r="U25">
         <v>1.336495600684904</v>
       </c>
-      <c r="U25">
+      <c r="V25">
         <v>1.482338865393845</v>
       </c>
-      <c r="V25" t="s">
-        <v>43</v>
-      </c>
-      <c r="W25">
+      <c r="W25" t="s">
+        <v>44</v>
+      </c>
+      <c r="X25" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y25">
         <v>7.778228198447484E-65</v>
       </c>
-      <c r="X25">
+      <c r="Z25">
         <v>9.333873838136981E-64</v>
       </c>
-      <c r="Y25">
-        <v>12</v>
-      </c>
-      <c r="Z25">
+      <c r="AA25">
+        <v>12</v>
+      </c>
+      <c r="AB25">
         <v>200269</v>
       </c>
-      <c r="AA25" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB25" t="s">
-        <v>50</v>
-      </c>
       <c r="AC25" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="AD25" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="AE25" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="AF25" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG25">
+        <v>81</v>
+      </c>
+      <c r="AG25" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI25">
         <v>0.3421932552448879</v>
       </c>
-      <c r="AH25">
+      <c r="AJ25">
         <v>1.408032380865063</v>
       </c>
-      <c r="AI25">
+      <c r="AK25">
         <v>1.336964124938389</v>
       </c>
-      <c r="AJ25">
+      <c r="AL25">
         <v>1.482878372413993</v>
       </c>
-      <c r="AK25" t="s">
-        <v>43</v>
-      </c>
-      <c r="AL25">
+      <c r="AM25" t="s">
+        <v>44</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>68</v>
+      </c>
+      <c r="AO25">
         <v>5.96322680502565E-65</v>
       </c>
-      <c r="AM25">
+      <c r="AP25">
         <v>7.155872166030781E-64</v>
       </c>
-      <c r="AN25">
-        <v>12</v>
-      </c>
-      <c r="AO25">
+      <c r="AQ25">
+        <v>12</v>
+      </c>
+      <c r="AR25">
         <v>200251</v>
       </c>
-      <c r="AP25" t="s">
-        <v>47</v>
-      </c>
-      <c r="AQ25" t="s">
-        <v>50</v>
-      </c>
-      <c r="AR25" t="s">
-        <v>51</v>
-      </c>
       <c r="AS25" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="AT25" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="AU25" t="s">
-        <v>20</v>
-      </c>
-      <c r="AV25">
+        <v>76</v>
+      </c>
+      <c r="AV25" t="s">
+        <v>81</v>
+      </c>
+      <c r="AW25" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX25" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY25">
         <v>0.3411524156167463</v>
       </c>
-      <c r="AW25">
+      <c r="AZ25">
         <v>1.406567607394727</v>
       </c>
-      <c r="AX25">
+      <c r="BA25">
         <v>1.33557432932464</v>
       </c>
-      <c r="AY25">
+      <c r="BB25">
         <v>1.481334576992477</v>
       </c>
-      <c r="AZ25" t="s">
-        <v>67</v>
-      </c>
-      <c r="BA25">
+      <c r="BC25" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD25" t="s">
+        <v>182</v>
+      </c>
+      <c r="BE25">
         <v>1.435234813179442E-64</v>
       </c>
-      <c r="BB25">
+      <c r="BF25">
         <v>1.722281775815331E-63</v>
       </c>
-      <c r="BC25">
-        <v>12</v>
-      </c>
-      <c r="BD25">
+      <c r="BG25">
+        <v>12</v>
+      </c>
+      <c r="BH25">
         <v>200238</v>
       </c>
-      <c r="BE25" t="s">
-        <v>47</v>
-      </c>
-      <c r="BF25" t="s">
-        <v>50</v>
-      </c>
-      <c r="BG25" t="s">
-        <v>51</v>
-      </c>
-      <c r="BH25" t="s">
-        <v>56</v>
-      </c>
       <c r="BI25" t="s">
-        <v>59</v>
+        <v>72</v>
+      </c>
+      <c r="BJ25" t="s">
+        <v>75</v>
+      </c>
+      <c r="BK25" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL25" t="s">
+        <v>81</v>
+      </c>
+      <c r="BM25" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="26" spans="1:61">
+    <row r="26" spans="1:65">
       <c r="A26" s="1">
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C26">
         <v>-0.2303676074852241</v>
@@ -5410,177 +5939,189 @@
         <v>1.253230793751302</v>
       </c>
       <c r="G26" t="s">
-        <v>44</v>
-      </c>
-      <c r="H26">
+        <v>45</v>
+      </c>
+      <c r="H26" t="s">
+        <v>69</v>
+      </c>
+      <c r="I26">
         <v>0.1932499411070835</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>2.318999293285002</v>
       </c>
-      <c r="J26">
-        <v>12</v>
-      </c>
       <c r="K26">
+        <v>12</v>
+      </c>
+      <c r="L26">
         <v>201921</v>
       </c>
-      <c r="L26" t="s">
-        <v>48</v>
-      </c>
       <c r="M26" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="N26" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="O26" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="P26" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="Q26" t="s">
-        <v>21</v>
-      </c>
-      <c r="R26">
+        <v>83</v>
+      </c>
+      <c r="R26" t="s">
+        <v>22</v>
+      </c>
+      <c r="S26">
         <v>-0.05630152239113311</v>
       </c>
-      <c r="S26">
+      <c r="T26">
         <v>0.9452540776471139</v>
       </c>
-      <c r="T26">
+      <c r="U26">
         <v>0.8395541250803163</v>
       </c>
-      <c r="U26">
+      <c r="V26">
         <v>1.064261665348876</v>
       </c>
-      <c r="V26" t="s">
-        <v>74</v>
-      </c>
-      <c r="W26">
+      <c r="W26" t="s">
+        <v>99</v>
+      </c>
+      <c r="X26" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y26">
         <v>0.2213413680063837</v>
       </c>
-      <c r="X26">
+      <c r="Z26">
         <v>2.656096416076605</v>
       </c>
-      <c r="Y26">
-        <v>12</v>
-      </c>
-      <c r="Z26">
+      <c r="AA26">
+        <v>12</v>
+      </c>
+      <c r="AB26">
         <v>201950</v>
       </c>
-      <c r="AA26" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB26" t="s">
-        <v>50</v>
-      </c>
       <c r="AC26" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="AD26" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="AE26" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="AF26" t="s">
-        <v>21</v>
-      </c>
-      <c r="AG26">
+        <v>82</v>
+      </c>
+      <c r="AG26" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI26">
         <v>-0.208145233577326</v>
       </c>
-      <c r="AH26">
+      <c r="AJ26">
         <v>0.8120890855439103</v>
       </c>
-      <c r="AI26">
+      <c r="AK26">
         <v>0.5434775204703028</v>
       </c>
-      <c r="AJ26">
+      <c r="AL26">
         <v>1.213460829601288</v>
       </c>
-      <c r="AK26" t="s">
-        <v>89</v>
-      </c>
-      <c r="AL26">
+      <c r="AM26" t="s">
+        <v>134</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>152</v>
+      </c>
+      <c r="AO26">
         <v>0.181891323570274</v>
       </c>
-      <c r="AM26">
+      <c r="AP26">
         <v>2.182695882843289</v>
       </c>
-      <c r="AN26">
-        <v>12</v>
-      </c>
-      <c r="AO26">
+      <c r="AQ26">
+        <v>12</v>
+      </c>
+      <c r="AR26">
         <v>201931</v>
       </c>
-      <c r="AP26" t="s">
-        <v>48</v>
-      </c>
-      <c r="AQ26" t="s">
-        <v>50</v>
-      </c>
-      <c r="AR26" t="s">
-        <v>51</v>
-      </c>
       <c r="AS26" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="AT26" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="AU26" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV26">
+        <v>76</v>
+      </c>
+      <c r="AV26" t="s">
+        <v>82</v>
+      </c>
+      <c r="AW26" t="s">
+        <v>83</v>
+      </c>
+      <c r="AX26" t="s">
+        <v>22</v>
+      </c>
+      <c r="AY26">
         <v>-0.2682042741775231</v>
       </c>
-      <c r="AW26">
+      <c r="AZ26">
         <v>0.7647515461529244</v>
       </c>
-      <c r="AX26">
+      <c r="BA26">
         <v>0.5098636821655436</v>
       </c>
-      <c r="AY26">
+      <c r="BB26">
         <v>1.147061357379441</v>
       </c>
-      <c r="AZ26" t="s">
-        <v>101</v>
-      </c>
-      <c r="BA26">
+      <c r="BC26" t="s">
+        <v>165</v>
+      </c>
+      <c r="BD26" t="s">
+        <v>183</v>
+      </c>
+      <c r="BE26">
         <v>0.08836548003667032</v>
       </c>
-      <c r="BB26">
+      <c r="BF26">
         <v>1.060385760440044</v>
       </c>
-      <c r="BC26">
-        <v>12</v>
-      </c>
-      <c r="BD26">
+      <c r="BG26">
+        <v>12</v>
+      </c>
+      <c r="BH26">
         <v>201919</v>
       </c>
-      <c r="BE26" t="s">
-        <v>48</v>
-      </c>
-      <c r="BF26" t="s">
-        <v>50</v>
-      </c>
-      <c r="BG26" t="s">
-        <v>51</v>
-      </c>
-      <c r="BH26" t="s">
-        <v>57</v>
-      </c>
       <c r="BI26" t="s">
-        <v>58</v>
+        <v>73</v>
+      </c>
+      <c r="BJ26" t="s">
+        <v>75</v>
+      </c>
+      <c r="BK26" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL26" t="s">
+        <v>82</v>
+      </c>
+      <c r="BM26" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="27" spans="1:61">
+    <row r="27" spans="1:65">
       <c r="A27" s="1">
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C27">
         <v>-0.04716007517714168</v>
@@ -5595,177 +6136,189 @@
         <v>0.9844838230506546</v>
       </c>
       <c r="G27" t="s">
-        <v>45</v>
-      </c>
-      <c r="H27">
+        <v>46</v>
+      </c>
+      <c r="H27" t="s">
+        <v>70</v>
+      </c>
+      <c r="I27">
         <v>0.0001163618184668492</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>0.001396341821602191</v>
       </c>
-      <c r="J27">
-        <v>12</v>
-      </c>
       <c r="K27">
+        <v>12</v>
+      </c>
+      <c r="L27">
         <v>201921</v>
       </c>
-      <c r="L27" t="s">
-        <v>48</v>
-      </c>
       <c r="M27" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="N27" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="O27" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="P27" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="Q27" t="s">
-        <v>20</v>
-      </c>
-      <c r="R27">
+        <v>83</v>
+      </c>
+      <c r="R27" t="s">
+        <v>21</v>
+      </c>
+      <c r="S27">
         <v>-0.0473688924304504</v>
       </c>
-      <c r="S27">
+      <c r="T27">
         <v>0.9537355068803121</v>
       </c>
-      <c r="T27">
+      <c r="U27">
         <v>0.9241447642488395</v>
       </c>
-      <c r="U27">
+      <c r="V27">
         <v>0.9842737331565075</v>
       </c>
-      <c r="V27" t="s">
-        <v>45</v>
-      </c>
-      <c r="W27">
+      <c r="W27" t="s">
+        <v>46</v>
+      </c>
+      <c r="X27" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y27">
         <v>0.0001082581529630629</v>
       </c>
-      <c r="X27">
+      <c r="Z27">
         <v>0.001299097835556755</v>
       </c>
-      <c r="Y27">
-        <v>12</v>
-      </c>
-      <c r="Z27">
+      <c r="AA27">
+        <v>12</v>
+      </c>
+      <c r="AB27">
         <v>201950</v>
       </c>
-      <c r="AA27" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB27" t="s">
-        <v>50</v>
-      </c>
       <c r="AC27" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="AD27" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="AE27" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="AF27" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG27">
+        <v>82</v>
+      </c>
+      <c r="AG27" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI27">
         <v>-0.04709152010063291</v>
       </c>
-      <c r="AH27">
+      <c r="AJ27">
         <v>0.9540000834112933</v>
       </c>
-      <c r="AI27">
+      <c r="AK27">
         <v>0.9243969164070285</v>
       </c>
-      <c r="AJ27">
+      <c r="AL27">
         <v>0.984551271207415</v>
       </c>
-      <c r="AK27" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL27">
+      <c r="AM27" t="s">
+        <v>46</v>
+      </c>
+      <c r="AN27" t="s">
+        <v>153</v>
+      </c>
+      <c r="AO27">
         <v>0.0001190516897981216</v>
       </c>
-      <c r="AM27">
+      <c r="AP27">
         <v>0.001428620277577459</v>
       </c>
-      <c r="AN27">
-        <v>12</v>
-      </c>
-      <c r="AO27">
+      <c r="AQ27">
+        <v>12</v>
+      </c>
+      <c r="AR27">
         <v>201931</v>
       </c>
-      <c r="AP27" t="s">
-        <v>48</v>
-      </c>
-      <c r="AQ27" t="s">
-        <v>50</v>
-      </c>
-      <c r="AR27" t="s">
-        <v>51</v>
-      </c>
       <c r="AS27" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="AT27" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="AU27" t="s">
-        <v>20</v>
-      </c>
-      <c r="AV27">
+        <v>76</v>
+      </c>
+      <c r="AV27" t="s">
+        <v>82</v>
+      </c>
+      <c r="AW27" t="s">
+        <v>83</v>
+      </c>
+      <c r="AX27" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY27">
         <v>-0.04682912850249191</v>
       </c>
-      <c r="AW27">
+      <c r="AZ27">
         <v>0.954250437861822</v>
       </c>
-      <c r="AX27">
+      <c r="BA27">
         <v>0.9246361579940167</v>
       </c>
-      <c r="AY27">
+      <c r="BB27">
         <v>0.9848132049421449</v>
       </c>
-      <c r="AZ27" t="s">
-        <v>45</v>
-      </c>
-      <c r="BA27">
+      <c r="BC27" t="s">
+        <v>46</v>
+      </c>
+      <c r="BD27" t="s">
+        <v>184</v>
+      </c>
+      <c r="BE27">
         <v>0.0001301416172477553</v>
       </c>
-      <c r="BB27">
+      <c r="BF27">
         <v>0.001561699406973064</v>
       </c>
-      <c r="BC27">
-        <v>12</v>
-      </c>
-      <c r="BD27">
+      <c r="BG27">
+        <v>12</v>
+      </c>
+      <c r="BH27">
         <v>201919</v>
       </c>
-      <c r="BE27" t="s">
-        <v>48</v>
-      </c>
-      <c r="BF27" t="s">
-        <v>50</v>
-      </c>
-      <c r="BG27" t="s">
-        <v>51</v>
-      </c>
-      <c r="BH27" t="s">
-        <v>57</v>
-      </c>
       <c r="BI27" t="s">
-        <v>58</v>
+        <v>73</v>
+      </c>
+      <c r="BJ27" t="s">
+        <v>75</v>
+      </c>
+      <c r="BK27" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL27" t="s">
+        <v>82</v>
+      </c>
+      <c r="BM27" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B1:P1"/>
-    <mergeCell ref="Q1:AE1"/>
-    <mergeCell ref="AF1:AT1"/>
-    <mergeCell ref="AU1:BI1"/>
+    <mergeCell ref="B1:Q1"/>
+    <mergeCell ref="R1:AG1"/>
+    <mergeCell ref="AH1:AW1"/>
+    <mergeCell ref="AX1:BM1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5773,10 +6326,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y15"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:29">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -5785,35 +6338,39 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
-      <c r="Q1" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
+      <c r="T1" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="U1" s="1"/>
-      <c r="V1" s="1" t="s">
-        <v>102</v>
-      </c>
+      <c r="V1" s="1"/>
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
+      <c r="Z1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:29">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>4</v>
@@ -5822,1004 +6379,1160 @@
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>103</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>104</v>
+        <v>186</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>105</v>
+        <v>187</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="J2" s="1" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="P2" s="1" t="s">
-        <v>105</v>
+        <v>10</v>
       </c>
       <c r="Q2" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="V2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="W2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="X2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="AC2" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="3" spans="1:25" hidden="1"/>
-    <row r="4" spans="1:25">
+    <row r="3" spans="1:29" hidden="1"/>
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
-        <v>118</v>
+        <v>189</v>
       </c>
       <c r="F4" t="s">
-        <v>127</v>
+        <v>201</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="H4" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="I4" t="s">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="J4" t="s">
-        <v>151</v>
+        <v>100</v>
       </c>
       <c r="K4" t="s">
-        <v>158</v>
+        <v>222</v>
       </c>
       <c r="L4" t="s">
-        <v>19</v>
+        <v>234</v>
       </c>
       <c r="M4" t="s">
-        <v>75</v>
+        <v>241</v>
       </c>
       <c r="N4" t="s">
-        <v>170</v>
+        <v>20</v>
       </c>
       <c r="O4" t="s">
-        <v>181</v>
+        <v>120</v>
       </c>
       <c r="P4" t="s">
-        <v>188</v>
+        <v>135</v>
       </c>
       <c r="Q4" t="s">
-        <v>19</v>
+        <v>253</v>
       </c>
       <c r="R4" t="s">
-        <v>90</v>
+        <v>264</v>
       </c>
       <c r="S4" t="s">
-        <v>200</v>
+        <v>271</v>
       </c>
       <c r="T4" t="s">
-        <v>211</v>
+        <v>20</v>
       </c>
       <c r="U4" t="s">
-        <v>218</v>
+        <v>154</v>
       </c>
       <c r="V4" t="s">
-        <v>19</v>
+        <v>166</v>
       </c>
       <c r="W4" t="s">
-        <v>46</v>
+        <v>283</v>
       </c>
       <c r="X4" t="s">
-        <v>49</v>
+        <v>294</v>
       </c>
       <c r="Y4" t="s">
-        <v>51</v>
+        <v>301</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
-        <v>119</v>
+        <v>190</v>
       </c>
       <c r="F5" t="s">
-        <v>128</v>
+        <v>202</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>211</v>
       </c>
       <c r="H5" t="s">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="I5" t="s">
-        <v>140</v>
+        <v>87</v>
       </c>
       <c r="J5" t="s">
-        <v>152</v>
+        <v>102</v>
       </c>
       <c r="K5" t="s">
-        <v>159</v>
+        <v>223</v>
       </c>
       <c r="L5" t="s">
-        <v>19</v>
+        <v>235</v>
       </c>
       <c r="M5" t="s">
-        <v>76</v>
+        <v>242</v>
       </c>
       <c r="N5" t="s">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c r="O5" t="s">
-        <v>182</v>
+        <v>121</v>
       </c>
       <c r="P5" t="s">
-        <v>189</v>
+        <v>137</v>
       </c>
       <c r="Q5" t="s">
-        <v>19</v>
+        <v>254</v>
       </c>
       <c r="R5" t="s">
-        <v>91</v>
+        <v>265</v>
       </c>
       <c r="S5" t="s">
-        <v>201</v>
+        <v>272</v>
       </c>
       <c r="T5" t="s">
-        <v>212</v>
+        <v>20</v>
       </c>
       <c r="U5" t="s">
-        <v>219</v>
+        <v>155</v>
       </c>
       <c r="V5" t="s">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="W5" t="s">
-        <v>47</v>
+        <v>284</v>
       </c>
       <c r="X5" t="s">
-        <v>49</v>
+        <v>295</v>
       </c>
       <c r="Y5" t="s">
-        <v>51</v>
+        <v>302</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>51</v>
       </c>
       <c r="E6" t="s">
-        <v>120</v>
+        <v>191</v>
       </c>
       <c r="F6" t="s">
-        <v>129</v>
+        <v>203</v>
       </c>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>212</v>
       </c>
       <c r="H6" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="I6" t="s">
-        <v>141</v>
+        <v>89</v>
       </c>
       <c r="J6" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="K6" t="s">
-        <v>160</v>
+        <v>224</v>
       </c>
       <c r="L6" t="s">
-        <v>19</v>
+        <v>203</v>
       </c>
       <c r="M6" t="s">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="N6" t="s">
-        <v>172</v>
+        <v>20</v>
       </c>
       <c r="O6" t="s">
-        <v>183</v>
+        <v>122</v>
       </c>
       <c r="P6" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="Q6" t="s">
-        <v>19</v>
+        <v>255</v>
       </c>
       <c r="R6" t="s">
-        <v>93</v>
+        <v>266</v>
       </c>
       <c r="S6" t="s">
-        <v>202</v>
+        <v>273</v>
       </c>
       <c r="T6" t="s">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="U6" t="s">
-        <v>220</v>
+        <v>157</v>
       </c>
       <c r="V6" t="s">
-        <v>19</v>
+        <v>170</v>
       </c>
       <c r="W6" t="s">
-        <v>48</v>
+        <v>285</v>
       </c>
       <c r="X6" t="s">
-        <v>49</v>
+        <v>203</v>
       </c>
       <c r="Y6" t="s">
-        <v>51</v>
+        <v>303</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>121</v>
+        <v>192</v>
       </c>
       <c r="F7" t="s">
-        <v>130</v>
+        <v>204</v>
       </c>
       <c r="G7" t="s">
-        <v>19</v>
+        <v>213</v>
       </c>
       <c r="H7" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="I7" t="s">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="J7" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="K7" t="s">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="L7" t="s">
-        <v>19</v>
+        <v>203</v>
       </c>
       <c r="M7" t="s">
-        <v>79</v>
+        <v>244</v>
       </c>
       <c r="N7" t="s">
-        <v>170</v>
+        <v>20</v>
       </c>
       <c r="O7" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="P7" t="s">
-        <v>191</v>
+        <v>141</v>
       </c>
       <c r="Q7" t="s">
-        <v>19</v>
+        <v>253</v>
       </c>
       <c r="R7" t="s">
-        <v>87</v>
+        <v>264</v>
       </c>
       <c r="S7" t="s">
+        <v>274</v>
+      </c>
+      <c r="T7" t="s">
+        <v>20</v>
+      </c>
+      <c r="U7" t="s">
+        <v>132</v>
+      </c>
+      <c r="V7" t="s">
+        <v>172</v>
+      </c>
+      <c r="W7" t="s">
+        <v>286</v>
+      </c>
+      <c r="X7" t="s">
         <v>203</v>
       </c>
-      <c r="T7" t="s">
-        <v>120</v>
-      </c>
-      <c r="U7" t="s">
-        <v>221</v>
-      </c>
-      <c r="V7" t="s">
-        <v>19</v>
-      </c>
-      <c r="W7" t="s">
-        <v>46</v>
-      </c>
-      <c r="X7" t="s">
-        <v>50</v>
-      </c>
       <c r="Y7" t="s">
-        <v>51</v>
+        <v>304</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="E8" t="s">
-        <v>122</v>
+        <v>193</v>
       </c>
       <c r="F8" t="s">
-        <v>131</v>
+        <v>205</v>
       </c>
       <c r="G8" t="s">
-        <v>19</v>
+        <v>214</v>
       </c>
       <c r="H8" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="I8" t="s">
+        <v>91</v>
+      </c>
+      <c r="J8" t="s">
+        <v>108</v>
+      </c>
+      <c r="K8" t="s">
+        <v>226</v>
+      </c>
+      <c r="L8" t="s">
+        <v>236</v>
+      </c>
+      <c r="M8" t="s">
+        <v>245</v>
+      </c>
+      <c r="N8" t="s">
+        <v>20</v>
+      </c>
+      <c r="O8" t="s">
+        <v>126</v>
+      </c>
+      <c r="P8" t="s">
         <v>143</v>
       </c>
-      <c r="J8" t="s">
-        <v>153</v>
-      </c>
-      <c r="K8" t="s">
-        <v>162</v>
-      </c>
-      <c r="L8" t="s">
-        <v>19</v>
-      </c>
-      <c r="M8" t="s">
-        <v>81</v>
-      </c>
-      <c r="N8" t="s">
-        <v>173</v>
-      </c>
-      <c r="O8" t="s">
-        <v>184</v>
-      </c>
-      <c r="P8" t="s">
-        <v>192</v>
-      </c>
       <c r="Q8" t="s">
-        <v>19</v>
+        <v>256</v>
       </c>
       <c r="R8" t="s">
-        <v>94</v>
+        <v>267</v>
       </c>
       <c r="S8" t="s">
-        <v>204</v>
+        <v>275</v>
       </c>
       <c r="T8" t="s">
-        <v>213</v>
+        <v>20</v>
       </c>
       <c r="U8" t="s">
-        <v>222</v>
+        <v>158</v>
       </c>
       <c r="V8" t="s">
-        <v>19</v>
+        <v>174</v>
       </c>
       <c r="W8" t="s">
-        <v>47</v>
+        <v>287</v>
       </c>
       <c r="X8" t="s">
-        <v>50</v>
+        <v>296</v>
       </c>
       <c r="Y8" t="s">
-        <v>51</v>
+        <v>305</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
-        <v>120</v>
+        <v>194</v>
       </c>
       <c r="F9" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
       <c r="G9" t="s">
-        <v>19</v>
+        <v>215</v>
       </c>
       <c r="H9" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="I9" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="J9" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="K9" t="s">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L9" t="s">
-        <v>19</v>
+        <v>203</v>
       </c>
       <c r="M9" t="s">
-        <v>82</v>
+        <v>246</v>
       </c>
       <c r="N9" t="s">
-        <v>174</v>
+        <v>20</v>
       </c>
       <c r="O9" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="P9" t="s">
-        <v>193</v>
+        <v>145</v>
       </c>
       <c r="Q9" t="s">
-        <v>19</v>
+        <v>257</v>
       </c>
       <c r="R9" t="s">
-        <v>95</v>
+        <v>203</v>
       </c>
       <c r="S9" t="s">
-        <v>205</v>
+        <v>276</v>
       </c>
       <c r="T9" t="s">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="U9" t="s">
-        <v>223</v>
+        <v>159</v>
       </c>
       <c r="V9" t="s">
-        <v>19</v>
+        <v>176</v>
       </c>
       <c r="W9" t="s">
-        <v>48</v>
+        <v>288</v>
       </c>
       <c r="X9" t="s">
-        <v>50</v>
+        <v>203</v>
       </c>
       <c r="Y9" t="s">
-        <v>51</v>
+        <v>306</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" t="s">
+        <v>195</v>
+      </c>
+      <c r="F10" t="s">
+        <v>206</v>
+      </c>
+      <c r="G10" t="s">
+        <v>216</v>
+      </c>
+      <c r="H10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" t="s">
+        <v>94</v>
+      </c>
+      <c r="J10" t="s">
         <v>112</v>
       </c>
-      <c r="E10" t="s">
-        <v>123</v>
-      </c>
-      <c r="F10" t="s">
-        <v>133</v>
-      </c>
-      <c r="G10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" t="s">
-        <v>69</v>
-      </c>
-      <c r="I10" t="s">
-        <v>145</v>
-      </c>
-      <c r="J10" t="s">
-        <v>154</v>
-      </c>
       <c r="K10" t="s">
-        <v>164</v>
+        <v>228</v>
       </c>
       <c r="L10" t="s">
-        <v>21</v>
+        <v>237</v>
       </c>
       <c r="M10" t="s">
-        <v>84</v>
+        <v>247</v>
       </c>
       <c r="N10" t="s">
-        <v>175</v>
+        <v>22</v>
       </c>
       <c r="O10" t="s">
-        <v>185</v>
+        <v>129</v>
       </c>
       <c r="P10" t="s">
-        <v>194</v>
+        <v>147</v>
       </c>
       <c r="Q10" t="s">
-        <v>21</v>
+        <v>258</v>
       </c>
       <c r="R10" t="s">
-        <v>96</v>
+        <v>268</v>
       </c>
       <c r="S10" t="s">
-        <v>206</v>
+        <v>277</v>
       </c>
       <c r="T10" t="s">
-        <v>214</v>
+        <v>22</v>
       </c>
       <c r="U10" t="s">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="V10" t="s">
-        <v>21</v>
+        <v>177</v>
       </c>
       <c r="W10" t="s">
-        <v>46</v>
+        <v>289</v>
       </c>
       <c r="X10" t="s">
-        <v>49</v>
+        <v>297</v>
       </c>
       <c r="Y10" t="s">
-        <v>51</v>
+        <v>307</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
-        <v>124</v>
+        <v>196</v>
       </c>
       <c r="F11" t="s">
-        <v>134</v>
+        <v>207</v>
       </c>
       <c r="G11" t="s">
-        <v>21</v>
+        <v>217</v>
       </c>
       <c r="H11" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="I11" t="s">
-        <v>146</v>
+        <v>95</v>
       </c>
       <c r="J11" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="K11" t="s">
-        <v>165</v>
+        <v>229</v>
       </c>
       <c r="L11" t="s">
-        <v>21</v>
+        <v>238</v>
       </c>
       <c r="M11" t="s">
-        <v>85</v>
+        <v>248</v>
       </c>
       <c r="N11" t="s">
-        <v>176</v>
+        <v>22</v>
       </c>
       <c r="O11" t="s">
-        <v>186</v>
+        <v>130</v>
       </c>
       <c r="P11" t="s">
-        <v>195</v>
+        <v>148</v>
       </c>
       <c r="Q11" t="s">
-        <v>21</v>
+        <v>259</v>
       </c>
       <c r="R11" t="s">
-        <v>97</v>
+        <v>269</v>
       </c>
       <c r="S11" t="s">
-        <v>207</v>
+        <v>278</v>
       </c>
       <c r="T11" t="s">
-        <v>215</v>
+        <v>22</v>
       </c>
       <c r="U11" t="s">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="V11" t="s">
-        <v>21</v>
+        <v>178</v>
       </c>
       <c r="W11" t="s">
-        <v>47</v>
+        <v>290</v>
       </c>
       <c r="X11" t="s">
-        <v>49</v>
+        <v>298</v>
       </c>
       <c r="Y11" t="s">
-        <v>51</v>
+        <v>308</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
-        <v>120</v>
+        <v>197</v>
       </c>
       <c r="F12" t="s">
-        <v>135</v>
+        <v>203</v>
       </c>
       <c r="G12" t="s">
-        <v>21</v>
+        <v>218</v>
       </c>
       <c r="H12" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="I12" t="s">
-        <v>147</v>
+        <v>96</v>
       </c>
       <c r="J12" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="K12" t="s">
-        <v>166</v>
+        <v>230</v>
       </c>
       <c r="L12" t="s">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="M12" t="s">
-        <v>86</v>
+        <v>249</v>
       </c>
       <c r="N12" t="s">
-        <v>177</v>
+        <v>22</v>
       </c>
       <c r="O12" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="P12" t="s">
-        <v>196</v>
+        <v>149</v>
       </c>
       <c r="Q12" t="s">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="R12" t="s">
-        <v>98</v>
+        <v>203</v>
       </c>
       <c r="S12" t="s">
-        <v>208</v>
+        <v>279</v>
       </c>
       <c r="T12" t="s">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="U12" t="s">
-        <v>226</v>
+        <v>162</v>
       </c>
       <c r="V12" t="s">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="W12" t="s">
-        <v>48</v>
+        <v>291</v>
       </c>
       <c r="X12" t="s">
-        <v>49</v>
+        <v>203</v>
       </c>
       <c r="Y12" t="s">
-        <v>51</v>
+        <v>309</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:29">
       <c r="A13" s="1">
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
-        <v>125</v>
+        <v>198</v>
       </c>
       <c r="F13" t="s">
-        <v>136</v>
+        <v>208</v>
       </c>
       <c r="G13" t="s">
-        <v>21</v>
+        <v>219</v>
       </c>
       <c r="H13" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="I13" t="s">
-        <v>148</v>
+        <v>97</v>
       </c>
       <c r="J13" t="s">
-        <v>156</v>
+        <v>116</v>
       </c>
       <c r="K13" t="s">
-        <v>167</v>
+        <v>231</v>
       </c>
       <c r="L13" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="M13" t="s">
-        <v>87</v>
+        <v>250</v>
       </c>
       <c r="N13" t="s">
-        <v>178</v>
+        <v>22</v>
       </c>
       <c r="O13" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="P13" t="s">
-        <v>197</v>
+        <v>150</v>
       </c>
       <c r="Q13" t="s">
-        <v>21</v>
+        <v>261</v>
       </c>
       <c r="R13" t="s">
-        <v>99</v>
+        <v>201</v>
       </c>
       <c r="S13" t="s">
-        <v>209</v>
+        <v>280</v>
       </c>
       <c r="T13" t="s">
-        <v>216</v>
+        <v>22</v>
       </c>
       <c r="U13" t="s">
-        <v>227</v>
+        <v>163</v>
       </c>
       <c r="V13" t="s">
-        <v>21</v>
+        <v>180</v>
       </c>
       <c r="W13" t="s">
-        <v>46</v>
+        <v>292</v>
       </c>
       <c r="X13" t="s">
-        <v>50</v>
+        <v>299</v>
       </c>
       <c r="Y13" t="s">
-        <v>51</v>
+        <v>310</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:29">
       <c r="A14" s="1">
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s">
-        <v>126</v>
+        <v>199</v>
       </c>
       <c r="F14" t="s">
-        <v>137</v>
+        <v>209</v>
       </c>
       <c r="G14" t="s">
-        <v>21</v>
+        <v>220</v>
       </c>
       <c r="H14" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="I14" t="s">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="J14" t="s">
-        <v>157</v>
+        <v>118</v>
       </c>
       <c r="K14" t="s">
-        <v>168</v>
+        <v>232</v>
       </c>
       <c r="L14" t="s">
-        <v>21</v>
+        <v>240</v>
       </c>
       <c r="M14" t="s">
-        <v>88</v>
+        <v>251</v>
       </c>
       <c r="N14" t="s">
-        <v>179</v>
+        <v>22</v>
       </c>
       <c r="O14" t="s">
-        <v>187</v>
+        <v>133</v>
       </c>
       <c r="P14" t="s">
-        <v>198</v>
+        <v>151</v>
       </c>
       <c r="Q14" t="s">
-        <v>21</v>
+        <v>262</v>
       </c>
       <c r="R14" t="s">
-        <v>100</v>
+        <v>270</v>
       </c>
       <c r="S14" t="s">
-        <v>210</v>
+        <v>281</v>
       </c>
       <c r="T14" t="s">
-        <v>217</v>
+        <v>22</v>
       </c>
       <c r="U14" t="s">
-        <v>228</v>
+        <v>164</v>
       </c>
       <c r="V14" t="s">
-        <v>21</v>
+        <v>181</v>
       </c>
       <c r="W14" t="s">
-        <v>47</v>
+        <v>293</v>
       </c>
       <c r="X14" t="s">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="Y14" t="s">
-        <v>51</v>
+        <v>311</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:29">
       <c r="A15" s="1">
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="s">
-        <v>117</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="F15" t="s">
-        <v>138</v>
+        <v>203</v>
       </c>
       <c r="G15" t="s">
-        <v>21</v>
+        <v>221</v>
       </c>
       <c r="H15" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="I15" t="s">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="J15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K15" t="s">
-        <v>169</v>
+        <v>233</v>
       </c>
       <c r="L15" t="s">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="M15" t="s">
-        <v>89</v>
+        <v>252</v>
       </c>
       <c r="N15" t="s">
-        <v>180</v>
+        <v>22</v>
       </c>
       <c r="O15" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="P15" t="s">
-        <v>199</v>
+        <v>152</v>
       </c>
       <c r="Q15" t="s">
-        <v>21</v>
+        <v>263</v>
       </c>
       <c r="R15" t="s">
-        <v>101</v>
+        <v>203</v>
       </c>
       <c r="S15" t="s">
-        <v>108</v>
+        <v>282</v>
       </c>
       <c r="T15" t="s">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="U15" t="s">
-        <v>229</v>
+        <v>165</v>
       </c>
       <c r="V15" t="s">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="W15" t="s">
-        <v>48</v>
+        <v>191</v>
       </c>
       <c r="X15" t="s">
-        <v>50</v>
+        <v>203</v>
       </c>
       <c r="Y15" t="s">
-        <v>51</v>
+        <v>312</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="L1:P1"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="V1:Y1"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="N1:S1"/>
+    <mergeCell ref="T1:Y1"/>
+    <mergeCell ref="Z1:AC1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
